--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -570,7 +570,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）と、認知症に関する見込量の算定をどこまで進められるかを整理したものです。**本資料は諮る資料であり、計画素案には入れていません。**（基準日 令和8年9月16日）</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）と、認知症に関する見込量の算定をどこまで進められるかを整理したものです。**案Bを採用し、計画素案へ反映しました（令和8年9月16日）。**（基準日 令和8年9月16日）</t>
         </is>
       </c>
     </row>
@@ -605,12 +605,12 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>位置づけは案Bを推す</t>
+          <t>位置づけは案Bを採用した（令和8年9月16日）</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>構成3町がそれぞれ市町村認知症施策推進計画を策定し、広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案です。認知症基本法の名宛人は「市町村」であり、広域連合は介護保険法上の保険者としての事務を共同処理する特別地方公共団体です。広域連合の計画に一体のものとして定めても、同法第13条の市町村計画としての効力は生じません。</t>
+          <t>構成3町がそれぞれ市町村認知症施策推進計画を策定し、広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案です。認知症基本法の名宛人は「市町村」であり、広域連合は介護保険法上の保険者としての事務を共同処理する特別地方公共団体です。広域連合の計画に一体のものとして定めても、同法第13条の市町村計画としての効力は生じません。**計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みです**（令和8年9月16日）。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -1278,7 +1278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>24段落</t>
+          <t>27段落</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>0件</t>
+          <t>1件</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>**言及がない。** 第1章第2節（計画の位置付け）は構成3町の老人福祉計画との切り分けと給付適正化計画（法第117条第2項第3号・第4号）を整理しているが、認知症は扱っていない</t>
+          <t>**令和8年9月16日に第1章第2節へ加えた（案Bの反映）。**従前は0件で、同節は給付適正化計画（法第117条第2項第3号・第4号）のみを整理していた</t>
         </is>
       </c>
     </row>
@@ -1372,17 +1372,17 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>第1章第3節の整合を図る計画の列挙</t>
+          <t>第1章第8節の整合を図る計画の列挙</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>「認知症施策推進計画」が他の計画と並べて掲げられている</t>
+          <t>「都道府県認知症施策推進計画」に改めた</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>**どの主体の計画かが書かれていない。**北海道の都道府県計画か、3町の市町村計画かが読み取れない</t>
+          <t>**令和8年9月16日に主体を明示した（案Bの反映）。**従前は「認知症施策推進計画」で、北海道の計画か3町の計画かが読み取れなかった</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>**実施主体が3町と広域連合の併記になっている。**位置づけ（03シート）が決まれば分けて書ける</t>
+          <t>**実施主体の併記は残している。**認知症総合支援事業の実施主体（確認事項No.130②）が決着していないため、案Bの反映では触れていない</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援	60</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援	61</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
@@ -1514,11 +1514,11 @@
         <v>4</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>北海道高齢者保健福祉計画・介護保険事業支援計画、医療計画・地域医療構想、認知症施策推進計画、地域福祉計画、健康増進計画、障がい福祉計画、地域防災計画、住宅施策等との整合を図ります。</t>
+          <t>認知症施策については、共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条が市町村認知症施策推進計画について定めています。同法は市町村を実施の主体としており、本広域連合は地方自治</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr"/>
@@ -1528,11 +1528,11 @@
         <v>5</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画とは別の計画として策定し、介護予防、生活支援、認知症、家族介護、医療・介護連携等は、共通指標と役割分担により接続します。詳細は資料編に示します。</t>
+          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
@@ -1542,11 +1542,11 @@
         <v>6</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>266</v>
+        <v>108</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>本表は地域包括ケア「見える化」システム（介護保険総合データベース）による各年度の値です。本節第7項の北海道「介護保険事業所一覧」（令和8年6月30日現在）とは出典と時点が異なるため、事業所数が一致しな</t>
+          <t>北海道高齢者保健福祉計画・介護保険事業支援計画、医療計画・地域医療構想、都道府県認知症施策推進計画、地域福祉計画、健康増進計画、障がい福祉計画、地域防災計画、住宅施策等との整合を図ります。</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
@@ -1556,11 +1556,11 @@
         <v>7</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>306</v>
+        <v>109</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>出典：北海道保健福祉部の各名簿（令和8年6月30日〜7月1日現在）、介護老人保健施設及び認知症対応型共同生活介護の一部は居所変更実態調査（令和7年4月1日現在）及び介護サービス情報公表システムの個別公</t>
+          <t>構成3町の高齢者福祉計画とは別の計画として策定し、介護予防、生活支援、認知症、家族介護、医療・介護連携等は、共通指標と役割分担により接続します。詳細は資料編に示します。</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr"/>
@@ -1570,11 +1570,11 @@
         <v>8</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>433</v>
+        <v>110</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第9期は5基本目標19施策を掲げましたが、計画全体の代表KPIは4項目です。施策体系の幅に対し成果指標の対象範囲が狭く、相談、医療介護連携、認知症、家族介護、住まい、供給、人材、質、BCP、財政の成果</t>
+          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。都道府県認知症施策推進計画の策定の状況は［要確認］です。</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr"/>
@@ -1584,11 +1584,11 @@
         <v>9</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>449</v>
+        <v>269</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の25箇所の運営主体は、住民団体17・社会福祉協議会6・介護関係施設事業所2で、住民個人が運営する通いの場は0箇所です。住民個人による運営は全国19.2％・北海道28.8％（令和2年度）あり</t>
+          <t>本表は地域包括ケア「見える化」システム（介護保険総合データベース）による各年度の値です。本節第7項の北海道「介護保険事業所一覧」（令和8年6月30日現在）とは出典と時点が異なるため、事業所数が一致しな</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1598,11 +1598,11 @@
         <v>10</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>478</v>
+        <v>309</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>総給付費は令和6年度96.3％、令和7年度97.8％で、いずれも計画の範囲内です。内訳では、施設サービスが計画を上回る一方、居住系サービスが2か年とも10ポイント以上下回っています。居住系の内訳は、特</t>
+          <t>出典：北海道保健福祉部の各名簿（令和8年6月30日〜7月1日現在）、介護老人保健施設及び認知症対応型共同生活介護の一部は居所変更実態調査（令和7年4月1日現在）及び介護サービス情報公表システムの個別公</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
@@ -1612,11 +1612,11 @@
         <v>11</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>486</v>
+        <v>436</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>このほか、第9期計画で計画値を0としながら実績のあるサービスが2つあります。認知症対応型通所介護は令和6年度・令和7年度とも延べ12人・約124万円、介護療養型医療施設は令和6年度に延べ1人・325,</t>
+          <t>第9期は5基本目標19施策を掲げましたが、計画全体の代表KPIは4項目です。施策体系の幅に対し成果指標の対象範囲が狭く、相談、医療介護連携、認知症、家族介護、住まい、供給、人材、質、BCP、財政の成果</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr"/>
@@ -1626,11 +1626,11 @@
         <v>12</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>563</v>
+        <v>452</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>令和6年度の25箇所の運営主体は、住民団体17・社会福祉協議会6・介護関係施設事業所2で、住民個人が運営する通いの場は0箇所です。住民個人による運営は全国19.2％・北海道28.8％（令和2年度）あり</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr"/>
@@ -1640,11 +1640,11 @@
         <v>13</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>567</v>
+        <v>481</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>認知症施策については、交付金評価の支援Ⅱが36.3点（全国54.5点の66.6％）で、「認知症地域支援推進員の業務の状況」が全国の33.9％、「認知症サポーター数」が41.7％、「認知症サポーターステ</t>
+          <t>総給付費は令和6年度96.3％、令和7年度97.8％で、いずれも計画の範囲内です。内訳では、施設サービスが計画を上回る一方、居住系サービスが2か年とも10ポイント以上下回っています。居住系の内訳は、特</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr"/>
@@ -1654,11 +1654,11 @@
         <v>14</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>569</v>
+        <v>489</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>一方、リハビリテーションの提供体制は当区域の強みです。理学療法士は全国の1.67倍、言語聴覚士は2.41倍が配置され、リハビリテーションマネジメント加算Ⅱ以上の算定は全国の2.66倍、認知症短期集中リ</t>
+          <t>このほか、第9期計画で計画値を0としながら実績のあるサービスが2つあります。認知症対応型通所介護は令和6年度・令和7年度とも延べ12人・約124万円、介護療養型医療施設は令和6年度に延べ1人・325,</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
@@ -1668,11 +1668,11 @@
         <v>15</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>認知症施策について、認知症地域支援推進員の業務内容を明確化し、サポーター養成とステップアップ講座を計画的に実施します。</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr"/>
@@ -1682,11 +1682,11 @@
         <v>16</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>認知症の通所・居住の受け皿が減少していることを踏まえ、既存の小規模多機能型居宅介護（5事業所・全国比4.00倍）との役割分担を検討します。</t>
+          <t>認知症施策については、交付金評価の支援Ⅱが36.3点（全国54.5点の66.6％）で、「認知症地域支援推進員の業務の状況」が全国の33.9％、「認知症サポーター数」が41.7％、「認知症サポーターステ</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr"/>
@@ -1696,11 +1696,11 @@
         <v>17</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>587</v>
+        <v>572</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の定員は縮小しています。介護老人福祉施設の定員は平成29年度234人から令和2年度以降160人へ31.6％減少し、要支援・要介護者1人当たりでは平成30年度0.126人から令和7年度0.0</t>
+          <t>一方、リハビリテーションの提供体制は当区域の強みです。理学療法士は全国の1.67倍、言語聴覚士は2.41倍が配置され、リハビリテーションマネジメント加算Ⅱ以上の算定は全国の2.66倍、認知症短期集中リ</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
@@ -1710,11 +1710,11 @@
         <v>18</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>661</v>
+        <v>581</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護被保険者証の電子資格確認が導入され、要介護認定等の申請の代行を行うことができる者に認知症対応型共同生活介護事業者等が追加されます（第</t>
+          <t>認知症施策について、認知症地域支援推進員の業務内容を明確化し、サポーター養成とステップアップ講座を計画的に実施します。本項は介護保険法第117条第3項による認知症である被保険者の地域における日常生活の</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
@@ -1724,11 +1724,11 @@
         <v>19</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>709</v>
+        <v>582</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>注）1人1月当たりの回（日）数は、要支援と要介護に分けて置いています。上表は介護給付（要介護1から要介護5まで）の分です。居宅療養管理指導、福祉用具貸与、特定福祉用具購入、住宅改修、小規模多機能型居宅</t>
+          <t>認知症の通所・居住の受け皿が減少していることを踏まえ、既存の小規模多機能型居宅介護（5事業所・全国比4.00倍）との役割分担を検討します。</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
@@ -1738,11 +1738,11 @@
         <v>20</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>719</v>
+        <v>590</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>注）「―」は令和7年度に要支援1・2の利用がないもの（介護予防訪問入浴介護・介護予防認知症対応型通所介護）及び月単位の包括報酬により回数の計上がないもの（介護予防通所リハビリテーション）です。介護予防</t>
+          <t>施設・居住系の定員は縮小しています。介護老人福祉施設の定員は平成29年度234人から令和2年度以降160人へ31.6％減少し、要支援・要介護者1人当たりでは平成30年度0.126人から令和7年度0.0</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
@@ -1752,11 +1752,11 @@
         <v>21</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>755</v>
+        <v>664</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護被保険者証の電子資格確認が導入され、要介護認定等の申請の代行を行うことができる者に認知症対応型共同生活介護事業者等が追加されます（第</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
@@ -1766,11 +1766,11 @@
         <v>22</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>760</v>
+        <v>712</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
+          <t>注）1人1月当たりの回（日）数は、要支援と要介護に分けて置いています。上表は介護給付（要介護1から要介護5まで）の分です。居宅療養管理指導、福祉用具貸与、特定福祉用具購入、住宅改修、小規模多機能型居宅</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr"/>
@@ -1780,11 +1780,11 @@
         <v>23</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>764</v>
+        <v>722</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
+          <t>注）「―」は令和7年度に要支援1・2の利用がないもの（介護予防訪問入浴介護・介護予防認知症対応型通所介護）及び月単位の包括報酬により回数の計上がないもの（介護予防通所リハビリテーション）です。介護予防</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr"/>
@@ -1794,17 +1794,59 @@
         <v>24</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>858</v>
+        <v>758</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
+          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>763</v>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>767</v>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>861</v>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
           <t>本計画は介護保険法に基づく広域連合の介護保険事業計画であり、構成3町の高齢者福祉計画とは分離して策定します。一方、介護予防、生活支援、認知症、家族介護、医療・介護連携等は相互に影響するため、次の役割分</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr"/>
-    </row>
-    <row r="39" ht="34" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>注）段落の番号は素案の先頭からの通し番号です。素案を改訂すると番号は動きます。本表は素案の実物（docx）から数えているため、素案を改めれば本表も追随します。</t>
         </is>
@@ -1815,7 +1857,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A42:D42"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1828,7 +1870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1929,7 +1971,8 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>**推す**</t>
+          <t>**採用**
+（令和8年9月16日）</t>
         </is>
       </c>
     </row>
@@ -2070,18 +2113,131 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>注）本資料は諮る資料であり、いずれの案も計画素案には反映していません（令和8年9月10日 発注者指示）。ご判断の後に素案へ反映します。</t>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>案Bによる計画素案への反映（令和8年9月16日・完了）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>箇所</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>反映した内容</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="76" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>第1章第2節　計画の位置付け</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>認知症基本法第13条が市町村認知症施策推進計画について定めること、同法は市町村を実施の主体としており、本広域連合は地方自治法第284条の規定により設けられ介護保険法上の保険者としての事務を共同処理するものであることから、市町村認知症施策推進計画は構成3町がそれぞれ策定すること、本計画は介護保険法第117条第3項により認知症である被保険者の地域における日常生活の支援に関する事項を定めること、両者の調和は資料2の役割分担及び共通KPIにより保つことを1段落で加えた。意見の聴取は、主体・方法・時期を3町と調整のうえ定めることとし［要協議］を残した。</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr"/>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>案B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="76" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>第1章第8節　関係計画等との関係</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>列挙していた「認知症施策推進計画」を「都道府県認知症施策推進計画」に改め、どの主体の計画かが読み取れるようにした。市町村認知症施策推進計画は構成3町が策定することを加え、都道府県認知症施策推進計画の策定の状況は［要確認］とした。</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>案B・No.149③</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="76" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>資料2（1）15領域の役割分担</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>「認知症施策」の行に、広域連合の側へ「本計画への位置づけ（第5章 基本目標2）、認知症総合支援事業」を、構成3町の側へ「市町村認知症施策推進計画の策定」を加えた。共通KPIはH10のまま。</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>案B（調和の手立て）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="76" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>第5章 基本目標2（3）施策の方向性</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>認知症施策の項が介護保険法第117条第3項による事項であること、構成3町が策定する市町村認知症施策推進計画とは資料2の役割分担及び共通KPIにより接続することを加えた。</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>案B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="62" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>注1）新たな節・章は起こしていません。いずれも既にある節への加筆です（令和8年9月10日 発注者指示）。
+注2）**認知症総合支援事業の実施主体（確認事項No.130②）と意見の聴取（同③）は決着していません。**素案では実施主体を従前どおり「3町・広域連合」と併記し、意見の聴取は［要協議］を残しています。
+注3）認知症基本法の条文を受領していないため、素案には条番号（第13条）のみを書き、項番号は書いていません（確認事項No.149）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A22:E22"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4073,7 +4229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4130,17 +4286,17 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>計画素案に認知症基本法への言及がないこと</t>
+          <t>計画素案に認知症基本法への言及があること（案Bの反映後）</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（893段落）から数えた</t>
+          <t>素案の実物（896段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>言及0件</t>
+          <t>言及1件</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -4165,7 +4321,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>24段落</t>
+          <t>27段落</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -4380,7 +4536,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>本資料が計画素案に反映されていないこと（諮る資料）</t>
+          <t>案Bが計画素案に反映されていること（令和8年9月16日）</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -4390,7 +4546,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>0件のまま</t>
+          <t>1件</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -4399,97 +4555,113 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="16" t="inlineStr"/>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>市町村認知症施策推進計画の主体が構成3町であることを素案に書いたこと</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>素案の実物から数えた</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>2箇所</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>意見の聴取が［要協議］のまま残されていること（No.130③は未決）</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>素案の実物から数えた</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>1箇所（いずれも［要協議］）</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="16" t="inlineStr"/>
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>11件</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>適合11件・不適合0件</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>13件</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>適合13件・不適合0件</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>点検の対象としていないもの</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="4" t="inlineStr"/>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="4" t="inlineStr"/>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>認知症基本法の条文</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>受領しておらず、外部にも接続できないため確かめられません。項番号・文言は［要確認］としています</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-    </row>
-    <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>国の認知症施策推進基本計画・北海道の認知症施策推進計画</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>いずれも受領しておらず、策定の状況も確認していません</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>認知症の人の数</t>
+          <t>認知症基本法の条文</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>把握しておらず、要介護認定における自立度によるほかありません。認定を受けていない方は含まれません</t>
+          <t>受領しておらず、外部にも接続できないため確かめられません。項番号・文言は［要確認］としています</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr"/>
@@ -4497,16 +4669,16 @@
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の量</t>
+          <t>国の認知症施策推進基本計画・北海道の認知症施策推進計画</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>実績を受領していないため算定できません（06シート）</t>
+          <t>いずれも受領しておらず、策定の状況も確認していません</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -4514,26 +4686,60 @@
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>3町における認知症カフェ・家族会の状況</t>
+          <t>認知症の人の数</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>把握していません。意見聴取の方法の選択に要ります（07シート）</t>
+          <t>把握しておらず、要介護認定における自立度によるほかありません。認定を受けていない方は含まれません</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
       <c r="E24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>認知症総合支援事業の量</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>実績を受領していないため算定できません（06シート）</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>3町における認知症カフェ・家族会の状況</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>把握していません。意見聴取の方法の選択に要ります（07シート）</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A20:E20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1278,7 +1278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>27段落</t>
+          <t>28段落</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援	61</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援	62</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
@@ -1542,7 +1542,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>7</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>8</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>9</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>10</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>12</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>566</v>
+        <v>582</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>570</v>
+        <v>586</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>17</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>572</v>
+        <v>588</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>18</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>19</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>20</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>21</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>664</v>
+        <v>680</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>22</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>712</v>
+        <v>728</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>23</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>722</v>
+        <v>738</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -1794,11 +1794,11 @@
         <v>24</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>758</v>
+        <v>775</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行いま</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr"/>
@@ -1808,11 +1808,11 @@
         <v>25</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>763</v>
+        <v>782</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
+          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr"/>
@@ -1822,11 +1822,11 @@
         <v>26</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>767</v>
+        <v>787</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
+          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr"/>
@@ -1836,17 +1836,31 @@
         <v>27</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>861</v>
+        <v>791</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>891</v>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
           <t>本計画は介護保険法に基づく広域連合の介護保険事業計画であり、構成3町の高齢者福祉計画とは分離して策定します。一方、介護予防、生活支援、認知症、家族介護、医療・介護連携等は相互に影響するため、次の役割分</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr"/>
-    </row>
-    <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>注）段落の番号は素案の先頭からの通し番号です。素案を改訂すると番号は動きます。本表は素案の実物（docx）から数えているため、素案を改めれば本表も追随します。</t>
         </is>
@@ -1857,7 +1871,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A43:D43"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4291,7 +4305,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（896段落）から数えた</t>
+          <t>素案の実物（926段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -4321,7 +4335,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>27段落</t>
+          <t>28段落</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -570,7 +570,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）と、認知症に関する見込量の算定をどこまで進められるかを整理したものです。**案Bを採用し、計画素案へ反映しました（令和8年9月16日）。**（基準日 令和8年9月16日）</t>
+          <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条の市町村認知症施策推進計画をどう扱うか（確認事項No.130）と、認知症に関する見込量の算定をどこまで進められるかを整理したものです。案Bを採用し、計画素案へ反映しました（令和8年9月16日）。（基準日 令和8年9月16日）</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>構成3町がそれぞれ市町村認知症施策推進計画を策定し、広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案です。認知症基本法の名宛人は「市町村」であり、広域連合は介護保険法上の保険者としての事務を共同処理する特別地方公共団体です。広域連合の計画に一体のものとして定めても、同法第13条の市町村計画としての効力は生じません。**計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みです**（令和8年9月16日）。</t>
+          <t>構成3町がそれぞれ市町村認知症施策推進計画を策定し、広域連合の計画は介護保険法第117条第3項の任意記載事項として認知症施策を掲げる案です。認知症基本法の名宛人は「市町村」であり、広域連合は介護保険法上の保険者としての事務を共同処理する特別地方公共団体です。広域連合の計画に一体のものとして定めても、同法第13条の市町村計画としての効力は生じません。計画素案 第1章第2節・第1章第8節・資料2・第5章 基本目標2に反映済みです（令和8年9月16日）。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>**現時点で認知症の人及び家族等の意見を聴いた資料は手元にありません。**調査①（在宅生活改善調査）は在宅の困難層に偏り代表性がなく（確認事項No.140）、健康とくらしの調査は要支援者・要介護者を含みません。策定委員会・運営協議会の構成が決まる前に方針を決める必要があります。</t>
+          <t>現時点で認知症の人及び家族等の意見を聴いた資料は手元にありません。調査①（在宅生活改善調査）は在宅の困難層に偏り代表性がなく（確認事項No.140）、健康とくらしの調査は要支援者・要介護者を含みません。策定委員会・運営協議会の構成が決まる前に方針を決める必要があります。</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業（包括的支援事業）の量です。決算の科目は4区分で6事業別の内訳が分からず、総合事業の実施状況に関する調査は包括的支援事業を含みません。交付金評価の得点は取組の有無であって「量」ではありません。認知症初期集中支援チームの活動件数、認知症地域支援推進員の配置人数、チームオレンジの数の資料のご提供を要します。</t>
+          <t>地域支援事業（包括的支援事業）の量です。決算の科目は4区分で6事業別の内訳が分からず、総合事業の実施状況に関する調査は包括的支援事業を含みません。交付金評価の得点は取組の有無であって「量」ではありません。令和8年9月25日受領の3町の地域包括支援センター事業実施報告書により取組の回数は町別に確認できましたが、費用の額の記載はありません。6事業別の事業費のご提供を要します。</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>「認知症対応型共同生活介護の実績は年率▲4.96％で減っている」としていましたが、これは**定員の縮小を趨勢と読んでいます**。令和4年度の落ち込み（前年比-14.7％）は1事業所の定員縮小によるもので、令和6年度から令和7年度は+3.7％と増に転じています。当方の算定（令和7年度基準）は直近の水準を起点としており、施策の向きとも合います。</t>
+          <t>「認知症対応型共同生活介護の実績は年率▲4.96％で減っている」としていましたが、これは定員の縮小を趨勢と読んでいます。令和4年度の落ち込み（前年比-14.7％）は1事業所の定員縮小によるもので、令和6年度から令和7年度は+3.7％と増に転じています。当方の算定（令和7年度基準）は直近の水準を起点としており、施策の向きとも合います。</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>**現時点で意見を聴いた資料は手元にありません。**調査①は在宅の困難層に偏り、健康とくらしの調査は要支援者・要介護者を含みません。**策定委員会・運営協議会の構成が決まる前に方針を決める必要があります。**委員として加えるか、意見交換会を別に開くか、既存の場（認知症カフェ・家族会）を通じるかの選択です（07シート）。</t>
+          <t>現時点で意見を聴いた資料は手元にありません。調査①は在宅の困難層に偏り、健康とくらしの調査は要支援者・要介護者を含みません。策定委員会・運営協議会の構成が決まる前に方針を決める必要があります。委員として加えるか、意見交換会を別に開くか、既存の場（認知症カフェ・家族会）を通じるかの選択です（07シート）。</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>**令和8年9月中**</t>
+          <t>令和8年9月中</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績</t>
+          <t>認知症総合支援事業の事業費（6事業別）</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業（包括的支援事業）の量の見込みが立ちません。決算の科目は4区分で6事業別の内訳が分からず、総合事業の実施状況に関する調査は包括的支援事業を含みません。認知症初期集中支援チームの活動件数、認知症地域支援推進員の配置人数、認知症サポーターの養成人数、チームオレンジの数を町別・年度別にご提供いただきたい（法第117条第2項第2号の記載事項）。</t>
+          <t>地域支援事業（包括的支援事業）の量の見込みが立ちません。決算の科目は4区分で6事業別の内訳が分かりません。令和8年9月25日受領の3町の地域包括支援センター事業実施報告書により、認知症初期集中支援チーム員会議・オレンジカフェ・サポーター養成講座の回数は町別に確認できましたが、費用の額の記載はありません。6事業別の事業費と、認知症サポーターの養成人数・チームオレンジの数を町別・年度別にご提供いただきたい（法第117条第2項第2号の記載事項）。東神楽町の実施報告書は量の欄が第1号被保険者数であり回数が分かりません。</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1111,7 +1111,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>当方が確認できている範囲で、法の規定と当広域連合の立場を整理します。**条文を受領していないため、項番号・文言は［要確認］です。**</t>
+          <t>当方が確認できている範囲で、法の規定と当広域連合の立場を整理します。条文を受領していないため、項番号・文言は［要確認］です。</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>**名宛人は「市町村」である。**策定は努力義務とされる［要確認］。</t>
+          <t>名宛人は「市町村」である。策定は努力義務とされる［要確認］。</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>**広域連合は「市町村」に当たらない。**広域連合は地方自治法第284条の規定により設けられ、介護保険法上の保険者としての事務を共同処理する特別地方公共団体である。認知症施策のうち介護保険の給付及び地域支援事業に属するものは広域連合の事務であるが、同法第13条の計画の主体は構成3町である。</t>
+          <t>広域連合は「市町村」に当たらない。広域連合は地方自治法第284条の規定により設けられ、介護保険法上の保険者としての事務を共同処理する特別地方公共団体である。認知症施策のうち介護保険の給付及び地域支援事業に属するものは広域連合の事務であるが、同法第13条の計画の主体は構成3町である。</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>**調和の相手方は広域連合の介護保険事業計画である。**3町が計画を策定する場合、広域連合の第10期計画と3町の計画の間で認知症施策の目標・指標をそろえる手立てが要る。</t>
+          <t>調和の相手方は広域連合の介護保険事業計画である。3町が計画を策定する場合、広域連合の第10期計画と3町の計画の間で認知症施策の目標・指標をそろえる手立てが要る。</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>**記述の追加では満たされない。**計画の主体が3町であれば3町が行うことになるが、広域連合の策定委員会・運営協議会でも同じ方が対象になり得る。重ねて依頼することのないよう調整を要する。</t>
+          <t>記述の追加では満たされない。計画の主体が3町であれば3町が行うことになるが、広域連合の策定委員会・運営協議会でも同じ方が対象になり得る。重ねて依頼することのないよう調整を要する。</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>**広域連合の第10期計画に認知症施策を掲げる根拠はこちらである。**認知症基本法第13条の計画とは別のものである。計画素案 第5章 基本目標2が該当する。</t>
+          <t>広域連合の第10期計画に認知症施策を掲げる根拠はこちらである。認知症基本法第13条の計画とは別のものである。計画素案 第5章 基本目標2が該当する。</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
           <t>28段落</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>分量としては不足していない</t>
         </is>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>**令和8年9月16日に第1章第2節へ加えた（案Bの反映）。**従前は0件で、同節は給付適正化計画（法第117条第2項第3号・第4号）のみを整理していた</t>
+          <t>令和8年9月16日に第1章第2節へ加えた（案Bの反映）。従前は0件で、同節は給付適正化計画（法第117条第2項第3号・第4号）のみを整理していた</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>**令和8年9月16日に主体を明示した（案Bの反映）。**従前は「認知症施策推進計画」で、北海道の計画か3町の計画かが読み取れなかった</t>
+          <t>令和8年9月16日に主体を明示した（案Bの反映）。従前は「認知症施策推進計画」で、北海道の計画か3町の計画かが読み取れなかった</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
           <t>「介護予防・生活支援・認知症・家族支援」として現状と課題・関連データ・施策の方向性・主な事業・達成目標を掲げている</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>施策としては置かれている。法第117条第3項の任意記載事項に当たる</t>
         </is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>**認知症の成果を測る指標が実質的にない。**H10は基本目標1と共通の指標であり、認知症固有のものではない</t>
+          <t>認知症の成果を測る指標が実質的にない。H10は基本目標1と共通の指標であり、認知症固有のものではない</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>**実施主体の併記は残している。**認知症総合支援事業の実施主体（確認事項No.130②）が決着していないため、案Bの反映では触れていない</t>
+          <t>実施主体の併記は残している。認知症総合支援事業の実施主体（確認事項No.130②）が決着していないため、案Bの反映では触れていない</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>**認知症基本法の名宛人は「市町村」であり広域連合は該当しない。**広域連合は介護保険法上の保険者としての事務を共同処理する特別地方公共団体であり、一体のものとして定めても同法第13条の市町村計画としての効力は生じない。法定の計画でないものを法定の計画として掲げることになる。</t>
+          <t>認知症基本法の名宛人は「市町村」であり広域連合は該当しない。広域連合は介護保険法上の保険者としての事務を共同処理する特別地方公共団体であり、一体のものとして定めても同法第13条の市町村計画としての効力は生じない。法定の計画でないものを法定の計画として掲げることになる。</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>**採用**
+          <t>採用
 （令和8年9月16日）</t>
         </is>
       </c>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>認知症初期集中支援推進事業・認知症地域支援推進員等配置事業は地域支援事業（包括的支援事業）であり、保険者の事務です。**計画の主体（3町）と事業の主体（広域連合）が分かれます。**事業の実施を3町へ委託しているかを含め整理を要します。確認事項No.130②に当たります。</t>
+          <t>認知症初期集中支援推進事業・認知症地域支援推進員等配置事業は地域支援事業（包括的支援事業）であり、保険者の事務です。計画の主体（3町）と事業の主体（広域連合）が分かれます。事業の実施を3町へ委託しているかを含め整理を要します。確認事項No.130②に当たります。</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr"/>
@@ -2123,7 +2123,7 @@
       <c r="D14" s="6" t="inlineStr"/>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>**令和8年9月中**</t>
+          <t>令和8年9月中</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>注1）新たな節・章は起こしていません。いずれも既にある節への加筆です（令和8年9月10日 発注者指示）。
-注2）**認知症総合支援事業の実施主体（確認事項No.130②）と意見の聴取（同③）は決着していません。**素案では実施主体を従前どおり「3町・広域連合」と併記し、意見の聴取は［要協議］を残しています。
+注2）認知症総合支援事業の実施主体（確認事項No.130②）と意見の聴取（同③）は決着していません。素案では実施主体を従前どおり「3町・広域連合」と併記し、意見の聴取は［要協議］を残しています。
 注3）認知症基本法の条文を受領していないため、素案には条番号（第13条）のみを書き、項番号は書いていません（確認事項No.149）。</t>
         </is>
       </c>
@@ -2474,7 +2474,7 @@
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>注1）割合は要介護認定を受けた方に占める割合です。認定を受けていない認知症の人は含まれません。
-注2）**割合は65.4％（平成24年4月末）から60.3％（令和6年10月末）へ低下していますが、認定者数が増えているため実数は増えています。**認定者数は令和6年度末1,993人・令和7年度末2,020人です。
+注2）割合は65.4％（平成24年4月末）から60.3％（令和6年10月末）へ低下していますが、認定者数が増えているため実数は増えています。認定者数は令和6年度末1,993人・令和7年度末2,020人です。
 注3）見える化システムの公表は令和6年10月末までです。令和7年度の値は未公表であり、実数は当方の推計です。</t>
         </is>
       </c>
@@ -2623,8 +2623,8 @@
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>注1）**令和4年度の落ち込み（前年比-14.7％）は1事業所の定員縮小によるものです。**区域全体の定員は平成28年から令和2年の115人が令和4年以降99人に減っています（計画素案 第6章第4節）。これを趨勢として将来へ延ばすと、定員の縮小をもう一度織り込むことになります。
-注2）**令和6年度から令和7年度は+3.7％と増に転じています。**当方の算定は令和7年度を基準年度としており、直近の水準を起点としています。
+          <t>注1）令和4年度の落ち込み（前年比-14.7％）は1事業所の定員縮小によるものです。区域全体の定員は平成28年から令和2年の115人が令和4年以降99人に減っています（計画素案 第6章第4節）。これを趨勢として将来へ延ばすと、定員の縮小をもう一度織り込むことになります。
+注2）令和6年度から令和7年度は+3.7％と増に転じています。当方の算定は令和7年度を基準年度としており、直近の水準を起点としています。
 注3）令和11年度の見込量85.2人は定員99人の86.1％、令和22年度の95.9人は96.9％です。第10期の間は定員に余裕があります。
 注4）第9期計画に対する実績は令和6年度86.2％・令和7年度90.1％で、いずれも計画を下回っています（計画素案 第3章）。</t>
         </is>
@@ -2774,8 +2774,8 @@
     <row r="25" ht="62" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>注1）**平成27年度に区域内から事業所が消滅しています。**令和5年度以降の月1.0人は区域外の事業所によるものです。「事業所ゼロ＝利用ゼロ」ではありません。
-注2）**第9期計画は計画値を0としていたため対計画比が算出されず、評価の対象から漏れていました**（計画素案 第3章）。実績は令和6年度・令和7年度とも延べ12人・約124万円です。
+          <t>注1）平成27年度に区域内から事業所が消滅しています。令和5年度以降の月1.0人は区域外の事業所によるものです。「事業所ゼロ＝利用ゼロ」ではありません。
+注2）第9期計画は計画値を0としていたため対計画比が算出されず、評価の対象から漏れていました（計画素案 第3章）。実績は令和6年度・令和7年度とも延べ12人・約124万円です。
 注3）第10期は計画値を0としません。当方の算定では令和11年度1.05人／月・給付費年約1,228,295円です。</t>
         </is>
       </c>
@@ -3475,7 +3475,7 @@
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>注1）11件で3町の得点が分かれています。同じ広域連合の区域内で取組の状況が異なることを示します。
-注2）**認知症総合支援事業は地域支援事業（包括的支援事業）であり保険者の事務ですが、交付金の評価は市町村単位です。**事業の実施を3町へ委託している場合、取組の差がそのまま得点の差になります。確認事項No.130②（実施主体との関係）に当たります。
+注2）認知症総合支援事業は地域支援事業（包括的支援事業）であり保険者の事務ですが、交付金の評価は市町村単位です。事業の実施を3町へ委託している場合、取組の差がそのまま得点の差になります。確認事項No.130②（実施主体との関係）に当たります。
 注3）得点の低い項目を計画の目標に据えるかどうかは、交付金の獲得を目的とするかという別の論点を含みます。第9期評価では交付金の得点を施策の評価に用いています。</t>
         </is>
       </c>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>**算定済み。** 要介護度別の利用率を令和7年度で固定し、要介護度別の認定者数の伸びを乗じたもの。給付費は令和11年度277,592,844円。定員99人に対し86.1％で余裕がある</t>
+          <t>算定済み。 要介護度別の利用率を令和7年度で固定し、要介護度別の認定者数の伸びを乗じたもの。給付費は令和11年度277,592,844円。定員99人に対し86.1％で余裕がある</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>**算定済み。** 区域内に事業所がないが区域外の事業所により給付が行われている。第9期は計画値0で評価から漏れていた。第10期は0としない</t>
+          <t>算定済み。 区域内に事業所がないが区域外の事業所により給付が行われている。第9期は計画値0で評価から漏れていた。第10期は0としない</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>**量の見込みが立たない。** 費用は地域支援事業費に含まれるが、決算の科目は4区分で6事業別の内訳が分からない。総合事業の実施状況に関する調査は包括的支援事業を含まない。交付金評価の得点は取組の有無であって量ではない</t>
+          <t>量の見込みが立たない。 費用は地域支援事業費に含まれるが、決算の科目は4区分で6事業別の内訳が分からない。総合事業の実施状況に関する調査は包括的支援事業を含まない。交付金評価の得点は取組の有無であって量ではない</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>**量の見込みが立たない。** 養成人数・ステップアップ講座の修了者数・チームオレンジの数の実績を受領していない。交付金評価では8年度年度に3町とも0点の項目がある</t>
+          <t>量の見込みが立たない。 養成人数・ステップアップ講座の修了者数・チームオレンジの数の実績を受領していない。交付金評価では8年度年度に3町とも0点の項目がある</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>**把握していない。** 要介護認定における自立度Ⅱ以上（割合は60.3％・令和6年10月末）によるほかない。認定を受けていない認知症の人は含まれない</t>
+          <t>把握していない。 要介護認定における自立度Ⅱ以上（割合は60.3％・令和6年10月末）によるほかない。認定を受けていない認知症の人は含まれない</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法に基づく施策（早期診断・早期対応、認知症地域支援推進員、サポーター等）を進めると、認知症対応型サービスの需要は増える向きに働きます。一方、共生の取組（地域で暮らし続ける）は居住系サービスの需要を減らす向きにも働きます。**2つの向きが打ち消し合うため、量を置けません。**</t>
+          <t>認知症基本法に基づく施策（早期診断・早期対応、認知症地域支援推進員、サポーター等）を進めると、認知症対応型サービスの需要は増える向きに働きます。一方、共生の取組（地域で暮らし続ける）は居住系サービスの需要を減らす向きにも働きます。2つの向きが打ち消し合うため、量を置けません。</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr"/>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>**補正の対象から外すことを推す**</t>
+          <t>補正の対象から外すことを推す</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項No.130③に対する設計案です。**記述の追加では満たされません。**策定委員会・運営協議会の構成が決まる前に方針を決める必要があります。</t>
+          <t>確認事項No.130③に対する設計案です。記述の追加では満たされません。策定委員会・運営協議会の構成が決まる前に方針を決める必要があります。</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>**代えられません。** 要介護度分布が在宅の認定者と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の困難層に偏っています（確認事項No.140）。また認知症の人ご本人の意見ではありません。</t>
+          <t>代えられません。 要介護度分布が在宅の認定者と食い違い（χ²＝43.5・自由度6。1％点16.81）、在宅の困難層に偏っています（確認事項No.140）。また認知症の人ご本人の意見ではありません。</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>**代えられません。** 施設への照会であり、ご本人・ご家族の意見ではありません。</t>
+          <t>代えられません。 施設への照会であり、ご本人・ご家族の意見ではありません。</t>
         </is>
       </c>
     </row>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>**代えられません。** 要支援者・要介護者を含みません（計画素案 第2章第4節）。認知症の人の意見は入っていません。</t>
+          <t>代えられません。 要支援者・要介護者を含みません（計画素案 第2章第4節）。認知症の人の意見は入っていません。</t>
         </is>
       </c>
     </row>
@@ -3995,14 +3995,14 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>**そのままでは代えられません。** 個別の支援の場であり、計画への意見の聴取とは目的が異なります。ただし地域課題として整理する経路はあります（地域ケア会議のKPI設計案 O2）。</t>
+          <t>そのままでは代えられません。 個別の支援の場であり、計画への意見の聴取とは目的が異なります。ただし地域課題として整理する経路はあります（地域ケア会議のKPI設計案 O2）。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>注）**現時点で認知症の人及び家族等の意見を聴いた資料は手元にありません。**第10期計画の策定の中で新たに行う必要があります。</t>
+          <t>注）現時点で認知症の人及び家族等の意見を聴いた資料は手元にありません。第10期計画の策定の中で新たに行う必要があります。</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>**構成が決まる前に方針を決める必要があります。**委員の選任は3町を通じて行うことになります。本人の参画は負担にもなるため、会議の進め方（資料の作り方・時間・同席者）の配慮を要します。</t>
+          <t>構成が決まる前に方針を決める必要があります。委員の選任は3町を通じて行うことになります。本人の参画は負担にもなるため、会議の進め方（資料の作り方・時間・同席者）の配慮を要します。</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>**当方は既存の場の有無を把握していません。**3町における認知症カフェ・家族会の状況のご提供を要します（09シート）。</t>
+          <t>当方は既存の場の有無を把握していません。3町における認知症カフェ・家族会の状況のご提供を要します（09シート）。</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>**令和8年9月中**</t>
+          <t>令和8年9月中</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>実績を受領していないため算定できません（06シート）</t>
+          <t>令和7年度の取組の回数は3町の実施報告書により確認できましたが、6事業別の事業費の記載がないため費用の額を置き直せません（06シート）。美瑛町の認知症初期集中支援推進事業は令和7年度の実績が0件であり、医師を確保できず休止中である旨が報告されています</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr"/>

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1278,7 +1278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>28段落</t>
+          <t>30段落</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -1696,11 +1696,11 @@
         <v>17</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>一方、リハビリテーションの提供体制は当区域の強みです。理学療法士は全国の1.67倍、言語聴覚士は2.41倍が配置され、リハビリテーションマネジメント加算Ⅱ以上の算定は全国の2.66倍、認知症短期集中リ</t>
+          <t>認知症初期集中支援推進事業は、構成3町がそれぞれ担当チームを設置していますが、実施の状況は町により異なります。令和7年度は、東川町が町立診療所の医師を専門医としてチーム員会議を1回開催した一方、美瑛町</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
@@ -1710,11 +1710,11 @@
         <v>18</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>認知症施策について、認知症地域支援推進員の業務内容を明確化し、サポーター養成とステップアップ講座を計画的に実施します。本項は介護保険法第117条第3項による認知症である被保険者の地域における日常生活の</t>
+          <t>一方、リハビリテーションの提供体制は当区域の強みです。理学療法士は全国の1.67倍、言語聴覚士は2.41倍が配置され、リハビリテーションマネジメント加算Ⅱ以上の算定は全国の2.66倍、認知症短期集中リ</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>認知症の通所・居住の受け皿が減少していることを踏まえ、既存の小規模多機能型居宅介護（5事業所・全国比4.00倍）との役割分担を検討します。</t>
+          <t>認知症施策について、認知症地域支援推進員の業務内容を明確化し、サポーター養成とステップアップ講座を計画的に実施します。本項は介護保険法第117条第3項による認知症である被保険者の地域における日常生活の</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
@@ -1738,11 +1738,11 @@
         <v>20</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の定員は縮小しています。介護老人福祉施設の定員は平成29年度234人から令和2年度以降160人へ31.6％減少し、要支援・要介護者1人当たりでは平成30年度0.126人から令和7年度0.0</t>
+          <t>認知症初期集中支援推進事業について、専門医の確保を含む担当チームの体制を3町及び広域連合で確かめ、休止している町の再開の見通しを整理します。あわせて、対応件数と会議の開催回数を町ごとに同じ様式で記録し</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
@@ -1752,11 +1752,11 @@
         <v>21</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護被保険者証の電子資格確認が導入され、要介護認定等の申請の代行を行うことができる者に認知症対応型共同生活介護事業者等が追加されます（第</t>
+          <t>認知症の通所・居住の受け皿が減少していることを踏まえ、既存の小規模多機能型居宅介護（5事業所・全国比4.00倍）との役割分担を検討します。</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
@@ -1766,11 +1766,11 @@
         <v>22</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>728</v>
+        <v>608</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>注）1人1月当たりの回（日）数は、要支援と要介護に分けて置いています。上表は介護給付（要介護1から要介護5まで）の分です。居宅療養管理指導、福祉用具貸与、特定福祉用具購入、住宅改修、小規模多機能型居宅</t>
+          <t>施設・居住系の定員は縮小しています。介護老人福祉施設の定員は平成29年度234人から令和2年度以降160人へ31.6％減少し、要支援・要介護者1人当たりでは平成30年度0.126人から令和7年度0.0</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr"/>
@@ -1780,11 +1780,11 @@
         <v>23</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>738</v>
+        <v>682</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>注）「―」は令和7年度に要支援1・2の利用がないもの（介護予防訪問入浴介護・介護予防認知症対応型通所介護）及び月単位の包括報酬により回数の計上がないもの（介護予防通所リハビリテーション）です。介護予防</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護被保険者証の電子資格確認が導入され、要介護認定等の申請の代行を行うことができる者に認知症対応型共同生活介護事業者等が追加されます（第</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr"/>
@@ -1794,11 +1794,11 @@
         <v>24</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>775</v>
+        <v>730</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行いま</t>
+          <t>注）1人1月当たりの回（日）数は、要支援と要介護に分けて置いています。上表は介護給付（要介護1から要介護5まで）の分です。居宅療養管理指導、福祉用具貸与、特定福祉用具購入、住宅改修、小規模多機能型居宅</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr"/>
@@ -1808,11 +1808,11 @@
         <v>25</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>782</v>
+        <v>740</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
+          <t>注）「―」は令和7年度に要支援1・2の利用がないもの（介護予防訪問入浴介護・介護予防認知症対応型通所介護）及び月単位の包括報酬により回数の計上がないもの（介護予防通所リハビリテーション）です。介護予防</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr"/>
@@ -1822,11 +1822,11 @@
         <v>26</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行いま</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr"/>
@@ -1836,11 +1836,11 @@
         <v>27</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
+          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr"/>
@@ -1850,17 +1850,45 @@
         <v>28</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>891</v>
+        <v>789</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
+          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>793</v>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>893</v>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
           <t>本計画は介護保険法に基づく広域連合の介護保険事業計画であり、構成3町の高齢者福祉計画とは分離して策定します。一方、介護予防、生活支援、認知症、家族介護、医療・介護連携等は相互に影響するため、次の役割分</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr"/>
-    </row>
-    <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>注）段落の番号は素案の先頭からの通し番号です。素案を改訂すると番号は動きます。本表は素案の実物（docx）から数えているため、素案を改めれば本表も追随します。</t>
         </is>
@@ -1868,10 +1896,10 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A45:D45"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A43:D43"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4305,7 +4333,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（926段落）から数えた</t>
+          <t>素案の実物（928段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -4335,7 +4363,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>28段落</t>
+          <t>30段落</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>1件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>認知症施策については、共生社会の実現を推進するための認知症基本法（令和5年法律第65号）第13条が市町村認知症施策推進計画について定めています。同法は市町村を実施の主体としており、本広域連合は地方自治</t>
+          <t>認知症施策については、共生社会の実現を推進するための認知症基本法（令和5年法律第65号）が、第11条で国の認知症施策推進基本計画を、第12条で都道府県認知症施策推進計画を、第13条で市町村認知症施策推</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr"/>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>北海道高齢者保健福祉計画・介護保険事業支援計画、医療計画・地域医療構想、都道府県認知症施策推進計画、地域福祉計画、健康増進計画、障がい福祉計画、地域防災計画、住宅施策等との整合を図ります。</t>
+          <t>認知症施策推進基本計画（認知症基本法第11条により国が定めるもの）、北海道高齢者保健福祉計画・介護保険事業支援計画、医療計画・地域医療構想、都道府県認知症施策推進計画、地域福祉計画、健康増進計画、障が</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。都道府県認知症施策推進計画の策定の状況は［要確認］です。</t>
+          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr"/>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>言及1件</t>
+          <t>言及2件</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>1件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1278,7 +1278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>30段落</t>
+          <t>36段落</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>2件</t>
+          <t>3件</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -1542,11 +1542,11 @@
         <v>6</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>認知症施策推進基本計画（認知症基本法第11条により国が定めるもの）、北海道高齢者保健福祉計画・介護保険事業支援計画、医療計画・地域医療構想、都道府県認知症施策推進計画、地域福祉計画、健康増進計画、障が</t>
+          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
@@ -1556,11 +1556,11 @@
         <v>7</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画とは別の計画として策定し、介護予防、生活支援、認知症、家族介護、医療・介護連携等は、共通指標と役割分担により接続します。詳細は資料編に示します。</t>
+          <t>認知症施策推進基本計画（認知症基本法第11条により国が定めるもの）、北海道高齢者保健福祉計画・介護保険事業支援計画、医療計画・地域医療構想、都道府県認知症施策推進計画、地域福祉計画、健康増進計画、障が</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr"/>
@@ -1570,11 +1570,11 @@
         <v>8</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況</t>
+          <t>構成3町の高齢者福祉計画とは別の計画として策定し、介護予防、生活支援、認知症、家族介護、医療・介護連携等は、共通指標と役割分担により接続します。詳細は資料編に示します。</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr"/>
@@ -1584,11 +1584,11 @@
         <v>9</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>276</v>
+        <v>119</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>本表は地域包括ケア「見える化」システム（介護保険総合データベース）による各年度の値です。本節第7項の北海道「介護保険事業所一覧」（令和8年6月30日現在）とは出典と時点が異なるため、事業所数が一致しな</t>
+          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1598,11 +1598,11 @@
         <v>10</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>316</v>
+        <v>142</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>出典：北海道保健福祉部の各名簿（令和8年6月30日〜7月1日現在）、介護老人保健施設及び認知症対応型共同生活介護の一部は居所変更実態調査（令和7年4月1日現在）及び介護サービス情報公表システムの個別公</t>
+          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
@@ -1612,11 +1612,11 @@
         <v>11</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>452</v>
+        <v>215</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第9期は5基本目標19施策を掲げましたが、計画全体の代表KPIは4項目です。施策体系の幅に対し成果指標の対象範囲が狭く、相談、医療介護連携、認知症、家族介護、住まい、供給、人材、質、BCP、財政の成果</t>
+          <t>【認知症高齢者の状況】</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr"/>
@@ -1626,11 +1626,11 @@
         <v>12</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>468</v>
+        <v>216</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の25箇所の運営主体は、住民団体17・社会福祉協議会6・介護関係施設事業所2で、住民個人が運営する通いの場は0箇所です。住民個人による運営は全国19.2％・北海道28.8％（令和2年度）あり</t>
+          <t>認定調査における認知症高齢者の日常生活自立度Ⅱ以上の方は、平成24年10月末1,190人から令和6年10月末1,498人へ308人（25.9％）増えています。一方、認定者に占める割合は65.5％から6</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr"/>
@@ -1640,11 +1640,11 @@
         <v>13</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>497</v>
+        <v>218</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>総給付費は令和6年度96.3％、令和7年度97.8％で、いずれも計画の範囲内です。内訳では、施設サービスが計画を上回る一方、居住系サービスが2か年とも10ポイント以上下回っています。居住系の内訳は、特</t>
+          <t>資料：地域包括ケア「見える化」システム B7系列（認知症高齢者自立度の状況）</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr"/>
@@ -1654,11 +1654,11 @@
         <v>14</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>505</v>
+        <v>220</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>このほか、第9期計画で計画値を0としながら実績のあるサービスが2つあります。認知症対応型通所介護は令和6年度・令和7年度とも延べ12人・約124万円、介護療養型医療施設は令和6年度に延べ1人・325,</t>
+          <t>認知症施策は、市町村認知症施策推進計画として構成3町が策定します（第1章第2節）。本計画には、介護保険法第117条第3項により認知症である被保険者の支援に関する事項を掲げ、認知症対応型共同生活介護等の</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
@@ -1668,11 +1668,11 @@
         <v>15</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>582</v>
+        <v>295</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>本表は地域包括ケア「見える化」システム（介護保険総合データベース）による各年度の値です。本節第7項の北海道「介護保険事業所一覧」（令和8年6月30日現在）とは出典と時点が異なるため、事業所数が一致しな</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr"/>
@@ -1682,11 +1682,11 @@
         <v>16</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>586</v>
+        <v>332</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>認知症施策については、交付金評価の支援Ⅱが36.3点（全国54.5点の66.6％）で、「認知症地域支援推進員の業務の状況」が全国の33.9％、「認知症サポーター数」が41.7％、「認知症サポーターステ</t>
+          <t>出典：北海道保健福祉部の各名簿（令和8年6月30日〜7月1日現在）、介護老人保健施設及び認知症対応型共同生活介護の一部は居所変更実態調査（令和7年4月1日現在）及び介護サービス情報公表システムの個別公</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr"/>
@@ -1696,11 +1696,11 @@
         <v>17</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>587</v>
+        <v>461</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>認知症初期集中支援推進事業は、構成3町がそれぞれ担当チームを設置していますが、実施の状況は町により異なります。令和7年度は、東川町が町立診療所の医師を専門医としてチーム員会議を1回開催した一方、美瑛町</t>
+          <t>第9期は5基本目標19施策を掲げましたが、計画全体の代表KPIは4項目です。施策体系の幅に対し成果指標の対象範囲が狭く、相談、医療介護連携、認知症、家族介護、住まい、供給、人材、質、BCP、財政の成果</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
@@ -1710,11 +1710,11 @@
         <v>18</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>589</v>
+        <v>477</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>一方、リハビリテーションの提供体制は当区域の強みです。理学療法士は全国の1.67倍、言語聴覚士は2.41倍が配置され、リハビリテーションマネジメント加算Ⅱ以上の算定は全国の2.66倍、認知症短期集中リ</t>
+          <t>令和6年度の25箇所の運営主体は、住民団体17・社会福祉協議会6・介護関係施設事業所2で、住民個人が運営する通いの場は0箇所です。住民個人による運営は全国19.2％・北海道28.8％（令和2年度）あり</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
@@ -1724,11 +1724,11 @@
         <v>19</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>598</v>
+        <v>506</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>認知症施策について、認知症地域支援推進員の業務内容を明確化し、サポーター養成とステップアップ講座を計画的に実施します。本項は介護保険法第117条第3項による認知症である被保険者の地域における日常生活の</t>
+          <t>総給付費は令和6年度96.3％、令和7年度97.8％で、いずれも計画の範囲内です。内訳では、施設サービスが計画を上回る一方、居住系サービスが2か年とも10ポイント以上下回っています。居住系の内訳は、特</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
@@ -1738,11 +1738,11 @@
         <v>20</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>599</v>
+        <v>514</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>認知症初期集中支援推進事業について、専門医の確保を含む担当チームの体制を3町及び広域連合で確かめ、休止している町の再開の見通しを整理します。あわせて、対応件数と会議の開催回数を町ごとに同じ様式で記録し</t>
+          <t>このほか、第9期計画で計画値を0としながら実績のあるサービスが2つあります。認知症対応型通所介護は令和6年度・令和7年度とも延べ12人・約124万円、介護療養型医療施設は令和6年度に延べ1人・325,</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
@@ -1752,11 +1752,11 @@
         <v>21</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>認知症の通所・居住の受け皿が減少していることを踏まえ、既存の小規模多機能型居宅介護（5事業所・全国比4.00倍）との役割分担を検討します。</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
@@ -1766,11 +1766,11 @@
         <v>22</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>608</v>
+        <v>591</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の定員は縮小しています。介護老人福祉施設の定員は平成29年度234人から令和2年度以降160人へ31.6％減少し、要支援・要介護者1人当たりでは平成30年度0.126人から令和7年度0.0</t>
+          <t>認知症施策については、交付金評価の支援Ⅱが36.3点（全国54.5点の66.6％）で、「認知症地域支援推進員の業務の状況」が全国の33.9％、「認知症サポーター数」が41.7％、「認知症サポーターステ</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr"/>
@@ -1780,11 +1780,11 @@
         <v>23</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>682</v>
+        <v>592</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護被保険者証の電子資格確認が導入され、要介護認定等の申請の代行を行うことができる者に認知症対応型共同生活介護事業者等が追加されます（第</t>
+          <t>認知症初期集中支援推進事業は、構成3町がそれぞれ担当チームを設置していますが、実施の状況は町により異なります。令和7年度は、東川町が町立診療所の医師を専門医としてチーム員会議を1回開催した一方、美瑛町</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr"/>
@@ -1794,11 +1794,11 @@
         <v>24</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>730</v>
+        <v>594</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>注）1人1月当たりの回（日）数は、要支援と要介護に分けて置いています。上表は介護給付（要介護1から要介護5まで）の分です。居宅療養管理指導、福祉用具貸与、特定福祉用具購入、住宅改修、小規模多機能型居宅</t>
+          <t>一方、リハビリテーションの提供体制は当区域の強みです。理学療法士は全国の1.67倍、言語聴覚士は2.41倍が配置され、リハビリテーションマネジメント加算Ⅱ以上の算定は全国の2.66倍、認知症短期集中リ</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr"/>
@@ -1808,11 +1808,11 @@
         <v>25</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>740</v>
+        <v>603</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>注）「―」は令和7年度に要支援1・2の利用がないもの（介護予防訪問入浴介護・介護予防認知症対応型通所介護）及び月単位の包括報酬により回数の計上がないもの（介護予防通所リハビリテーション）です。介護予防</t>
+          <t>認知症施策について、認知症地域支援推進員の業務内容を明確化し、サポーター養成とステップアップ講座を計画的に実施します。本項は介護保険法第117条第3項による認知症である被保険者の地域における日常生活の</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr"/>
@@ -1822,11 +1822,11 @@
         <v>26</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>777</v>
+        <v>604</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行いま</t>
+          <t>認知症初期集中支援推進事業について、専門医の確保を含む担当チームの体制を3町及び広域連合で確かめ、休止している町の再開の見通しを整理します。あわせて、対応件数と会議の開催回数を町ごとに同じ様式で記録し</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr"/>
@@ -1836,11 +1836,11 @@
         <v>27</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>784</v>
+        <v>605</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
+          <t>認知症の通所・居住の受け皿が減少していることを踏まえ、既存の小規模多機能型居宅介護（5事業所・全国比4.00倍）との役割分担を検討します。</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr"/>
@@ -1850,11 +1850,11 @@
         <v>28</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>789</v>
+        <v>613</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
+          <t>施設・居住系の定員は縮小しています。介護老人福祉施設の定員は平成29年度234人から令和2年度以降160人へ31.6％減少し、要支援・要介護者1人当たりでは平成30年度0.126人から令和7年度0.0</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr"/>
@@ -1864,11 +1864,11 @@
         <v>29</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>793</v>
+        <v>687</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護被保険者証の電子資格確認が導入され、要介護認定等の申請の代行を行うことができる者に認知症対応型共同生活介護事業者等が追加されます（第</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr"/>
@@ -1878,17 +1878,101 @@
         <v>30</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>893</v>
+        <v>735</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
+          <t>注）1人1月当たりの回（日）数は、要支援と要介護に分けて置いています。上表は介護給付（要介護1から要介護5まで）の分です。居宅療養管理指導、福祉用具貸与、特定福祉用具購入、住宅改修、小規模多機能型居宅</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>745</v>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>注）「―」は令和7年度に要支援1・2の利用がないもの（介護予防訪問入浴介護・介護予防認知症対応型通所介護）及び月単位の包括報酬により回数の計上がないもの（介護予防通所リハビリテーション）です。介護予防</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>782</v>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行いま</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>789</v>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr"/>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>794</v>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr"/>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>798</v>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>892</v>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
           <t>本計画は介護保険法に基づく広域連合の介護保険事業計画であり、構成3町の高齢者福祉計画とは分離して策定します。一方、介護予防、生活支援、認知症、家族介護、医療・介護連携等は相互に影響するため、次の役割分</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr"/>
-    </row>
-    <row r="45" ht="34" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr"/>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>注）段落の番号は素案の先頭からの通し番号です。素案を改訂すると番号は動きます。本表は素案の実物（docx）から数えているため、素案を改めれば本表も追随します。</t>
         </is>
@@ -1896,10 +1980,10 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A45:D45"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A51:D51"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4333,12 +4417,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（928段落）から数えた</t>
+          <t>素案の実物（927段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>言及2件</t>
+          <t>言及3件</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -4363,7 +4447,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>30段落</t>
+          <t>36段落</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -4588,7 +4672,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>2件</t>
+          <t>3件</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -4633,12 +4717,12 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>素案の実物から数えた</t>
+          <t>素案の実物から数えた（注記を除く）</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>1箇所（いずれも［要協議］）</t>
+          <t>本文1箇所（いずれも［要協議］）・注記1箇所</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1598,7 +1598,7 @@
         <v>10</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>12</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>17</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>18</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>19</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>20</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>21</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>22</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>23</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>24</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>25</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>26</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>27</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>28</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>29</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>30</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>31</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>32</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>33</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>34</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>36</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（927段落）から数えた</t>
+          <t>素案の実物（928段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -3694,7 +3694,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>算定済み。 要介護度別の利用率を令和7年度で固定し、要介護度別の認定者数の伸びを乗じたもの。給付費は令和11年度277,592,844円。定員99人に対し86.1％で余裕がある</t>
+          <t>算定済み。 要介護度別の利用率を令和7年度で固定し、要介護度別の認定者数の伸びを乗じたもの。給付費は令和11年度277,663,044円。定員99人に対し86.1％で余裕がある</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1962,7 +1962,7 @@
         <v>36</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>893</v>
+        <v>907</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（928段落）から数えた</t>
+          <t>素案の実物（942段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1278,7 +1278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>36段落</t>
+          <t>39段落</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -1906,11 +1906,11 @@
         <v>32</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>783</v>
+        <v>765</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行いま</t>
+          <t>【認知症総合支援事業の実施状況】</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr"/>
@@ -1920,11 +1920,11 @@
         <v>33</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>790</v>
+        <v>766</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
+          <t>認知症総合支援事業は包括的支援事業（社会保障充実分）として実施しています。事業ごとの利用者実人数及び事業費を把握できていないため量の見込みは掲げられません。構成3町の実施状況は次のとおりです。</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr"/>
@@ -1934,11 +1934,11 @@
         <v>34</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>795</v>
+        <v>768</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
+          <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではあり</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr"/>
@@ -1948,11 +1948,11 @@
         <v>35</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>799</v>
+        <v>788</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行いま</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr"/>
@@ -1962,17 +1962,59 @@
         <v>36</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>907</v>
+        <v>795</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
+          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>800</v>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>804</v>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>914</v>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
           <t>本計画は介護保険法に基づく広域連合の介護保険事業計画であり、構成3町の高齢者福祉計画とは分離して策定します。一方、介護予防、生活支援、認知症、家族介護、医療・介護連携等は相互に影響するため、次の役割分</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr"/>
-    </row>
-    <row r="51" ht="34" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54" ht="34" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>注）段落の番号は素案の先頭からの通し番号です。素案を改訂すると番号は動きます。本表は素案の実物（docx）から数えているため、素案を改めれば本表も追随します。</t>
         </is>
@@ -1983,7 +2025,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A54:D54"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4417,7 +4459,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（942段落）から数えた</t>
+          <t>素案の実物（949段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -4447,7 +4489,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>36段落</t>
+          <t>39段落</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1278,7 +1278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>39段落</t>
+          <t>40段落</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -1864,7 +1864,7 @@
         <v>29</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>30</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>31</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>32</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>33</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>34</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>36</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>37</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>38</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
@@ -2004,17 +2004,31 @@
         <v>39</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>914</v>
+        <v>877</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>916</v>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
           <t>本計画は介護保険法に基づく広域連合の介護保険事業計画であり、構成3町の高齢者福祉計画とは分離して策定します。一方、介護予防、生活支援、認知症、家族介護、医療・介護連携等は相互に影響するため、次の役割分</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr"/>
-    </row>
-    <row r="54" ht="34" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55" ht="34" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>注）段落の番号は素案の先頭からの通し番号です。素案を改訂すると番号は動きます。本表は素案の実物（docx）から数えているため、素案を改めれば本表も追随します。</t>
         </is>
@@ -2025,7 +2039,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A55:D55"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4459,7 +4473,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（949段落）から数えた</t>
+          <t>素案の実物（951段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -4489,7 +4503,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>39段落</t>
+          <t>40段落</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1278,7 +1278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>40段落</t>
+          <t>41段落</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援	62</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援	63</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
@@ -1668,7 +1668,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>17</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>18</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>19</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>20</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>21</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>588</v>
+        <v>604</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>22</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>592</v>
+        <v>608</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>23</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>593</v>
+        <v>609</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>24</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>595</v>
+        <v>611</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>25</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>26</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>27</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>606</v>
+        <v>622</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>28</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>614</v>
+        <v>630</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>29</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>689</v>
+        <v>706</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
@@ -1878,11 +1878,11 @@
         <v>30</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>737</v>
+        <v>746</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>注）1人1月当たりの回（日）数は、要支援と要介護に分けて置いています。上表は介護給付（要介護1から要介護5まで）の分です。居宅療養管理指導、福祉用具貸与、特定福祉用具購入、住宅改修、小規模多機能型居宅</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr"/>
@@ -1892,11 +1892,11 @@
         <v>31</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>注）「―」は令和7年度に要支援1・2の利用がないもの（介護予防訪問入浴介護・介護予防認知症対応型通所介護）及び月単位の包括報酬により回数の計上がないもの（介護予防通所リハビリテーション）です。介護予防</t>
+          <t>注）1人1月当たりの回（日）数は、要支援と要介護に分けて置いています。上表は介護給付（要介護1から要介護5まで）の分です。居宅療養管理指導、福祉用具貸与、特定福祉用具購入、住宅改修、小規模多機能型居宅</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr"/>
@@ -1906,11 +1906,11 @@
         <v>32</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>【認知症総合支援事業の実施状況】</t>
+          <t>注）「―」は令和7年度に要支援1・2の利用がないもの（介護予防訪問入浴介護・介護予防認知症対応型通所介護）及び月単位の包括報酬により回数の計上がないもの（介護予防通所リハビリテーション）です。介護予防</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr"/>
@@ -1920,11 +1920,11 @@
         <v>33</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>767</v>
+        <v>783</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業は包括的支援事業（社会保障充実分）として実施しています。事業ごとの利用者実人数及び事業費を把握できていないため量の見込みは掲げられません。構成3町の実施状況は次のとおりです。</t>
+          <t>【認知症総合支援事業の実施状況】</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr"/>
@@ -1934,11 +1934,11 @@
         <v>34</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>769</v>
+        <v>784</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではあり</t>
+          <t>認知症総合支援事業は包括的支援事業（社会保障充実分）として実施しています。事業ごとの利用者実人数及び事業費を把握できていないため量の見込みは掲げられません。構成3町の実施状況は次のとおりです。</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr"/>
@@ -1948,11 +1948,11 @@
         <v>35</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行いま</t>
+          <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではあり</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr"/>
@@ -1962,11 +1962,11 @@
         <v>36</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>796</v>
+        <v>807</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行いま</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr"/>
@@ -1976,11 +1976,11 @@
         <v>37</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>801</v>
+        <v>814</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
+          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr"/>
@@ -1990,11 +1990,11 @@
         <v>38</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>805</v>
+        <v>819</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
+          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr"/>
@@ -2004,11 +2004,11 @@
         <v>39</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>877</v>
+        <v>823</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr"/>
@@ -2018,17 +2018,31 @@
         <v>40</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>916</v>
+        <v>899</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>938</v>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
           <t>本計画は介護保険法に基づく広域連合の介護保険事業計画であり、構成3町の高齢者福祉計画とは分離して策定します。一方、介護予防、生活支援、認知症、家族介護、医療・介護連携等は相互に影響するため、次の役割分</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr"/>
-    </row>
-    <row r="55" ht="34" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56" ht="34" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>注）段落の番号は素案の先頭からの通し番号です。素案を改訂すると番号は動きます。本表は素案の実物（docx）から数えているため、素案を改めれば本表も追随します。</t>
         </is>
@@ -2037,9 +2051,9 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A56:D56"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A55:D55"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4473,7 +4487,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（951段落）から数えた</t>
+          <t>素案の実物（973段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -4503,7 +4517,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>40段落</t>
+          <t>41段落</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援	63</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援	67</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
@@ -1612,7 +1612,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>12</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>17</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>18</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>19</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>20</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>21</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>22</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>23</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>24</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>25</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>26</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>27</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>28</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>29</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>706</v>
+        <v>722</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>30</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>746</v>
+        <v>762</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>31</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>754</v>
+        <v>770</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>32</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>764</v>
+        <v>780</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>33</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>783</v>
+        <v>799</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>34</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>784</v>
+        <v>800</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>786</v>
+        <v>802</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>36</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>807</v>
+        <v>823</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>37</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>814</v>
+        <v>830</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>38</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>819</v>
+        <v>835</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>39</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>823</v>
+        <v>839</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>40</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>899</v>
+        <v>916</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>41</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>938</v>
+        <v>965</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（973段落）から数えた</t>
+          <t>素案の実物（1000段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1752,7 +1752,7 @@
         <v>21</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>22</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>23</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>24</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>25</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>26</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>27</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>28</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>29</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>30</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>31</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>32</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>33</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>34</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>36</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>37</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>38</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>39</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>40</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>41</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（1000段落）から数えた</t>
+          <t>素案の実物（1001段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1278,7 +1278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>41段落</t>
+          <t>45段落</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援	67</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援	70</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
+          <t>介護保険法以外の法律が市町村を名宛人として定める計画等についても、市町村認知症施策推進計画と同じ整理により、構成3町がそれぞれ定めます。老人福祉法第20条の8は市町村老人福祉計画を定めるものとし、同計</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
@@ -1542,11 +1542,11 @@
         <v>6</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は</t>
+          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
@@ -1556,11 +1556,11 @@
         <v>7</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>認知症施策推進基本計画（認知症基本法第11条により国が定めるもの）、北海道高齢者保健福祉計画・介護保険事業支援計画、医療計画・地域医療構想、都道府県認知症施策推進計画、地域福祉計画、健康増進計画、障が</t>
+          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr"/>
@@ -1570,11 +1570,11 @@
         <v>8</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画とは別の計画として策定し、介護予防、生活支援、認知症、家族介護、医療・介護連携等は、共通指標と役割分担により接続します。詳細は資料編に示します。</t>
+          <t>認知症施策推進基本計画（認知症基本法第11条により国が定めるもの）、北海道高齢者保健福祉計画・介護保険事業支援計画、医療計画・地域医療構想、都道府県認知症施策推進計画、地域福祉計画、健康増進計画、障が</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr"/>
@@ -1584,11 +1584,11 @@
         <v>9</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況</t>
+          <t>構成3町の高齢者福祉計画とは別の計画として策定し、介護予防、生活支援、認知症、家族介護、医療・介護連携等は、共通指標と役割分担により接続します。詳細は資料編に示します。構成3町の高齢者福祉計画は老人福</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1598,11 +1598,11 @@
         <v>10</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施</t>
+          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
@@ -1612,11 +1612,11 @@
         <v>11</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>224</v>
+        <v>147</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>【認知症高齢者の状況】</t>
+          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr"/>
@@ -1626,11 +1626,11 @@
         <v>12</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>225</v>
+        <v>148</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>認定調査における認知症高齢者の日常生活自立度Ⅱ以上の方は、平成24年10月末1,190人から令和6年10月末1,498人へ308人（25.9％）増えています。一方、認定者に占める割合は65.5％から6</t>
+          <t>あわせて、生産性向上の取組に係る委員会の設置についても、経過措置の終了により令和9年4月1日から義務となります。当広域連合において対象となるのは、小規模多機能型居宅介護5事業所、認知症対応型共同生活介</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr"/>
@@ -1640,11 +1640,11 @@
         <v>13</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>資料：地域包括ケア「見える化」システム B7系列（認知症高齢者自立度の状況）</t>
+          <t>【認知症高齢者の状況】</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr"/>
@@ -1654,11 +1654,11 @@
         <v>14</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>認知症施策は、市町村認知症施策推進計画として構成3町が策定します（第1章第2節）。本計画には、介護保険法第117条第3項により認知症である被保険者の支援に関する事項を掲げ、認知症対応型共同生活介護等の</t>
+          <t>認定調査における認知症高齢者の日常生活自立度Ⅱ以上の方は、平成24年10月末1,190人から令和6年10月末1,498人へ308人（25.9％）増えています。一方、認定者に占める割合は65.5％から6</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
@@ -1668,11 +1668,11 @@
         <v>15</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>311</v>
+        <v>233</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>本表は地域包括ケア「見える化」システム（介護保険総合データベース）による各年度の値です。本節第7項の北海道「介護保険事業所一覧」（令和8年6月30日現在）とは出典と時点が異なるため、事業所数が一致しな</t>
+          <t>資料：地域包括ケア「見える化」システム B7系列（認知症高齢者自立度の状況）</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr"/>
@@ -1682,11 +1682,11 @@
         <v>16</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>348</v>
+        <v>235</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>出典：北海道保健福祉部の各名簿（令和8年6月30日〜7月1日現在）、介護老人保健施設及び認知症対応型共同生活介護の一部は居所変更実態調査（令和7年4月1日現在）及び介護サービス情報公表システムの個別公</t>
+          <t>認知症施策は、市町村認知症施策推進計画として構成3町が策定します（第1章第2節）。本計画には、介護保険法第117条第3項により認知症である被保険者の支援に関する事項を掲げ、認知症対応型共同生活介護等の</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr"/>
@@ -1696,11 +1696,11 @@
         <v>17</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>477</v>
+        <v>318</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第9期は5基本目標19施策を掲げましたが、計画全体の代表KPIは4項目です。施策体系の幅に対し成果指標の対象範囲が狭く、相談、医療介護連携、認知症、家族介護、住まい、供給、人材、質、BCP、財政の成果</t>
+          <t>本表は地域包括ケア「見える化」システム（介護保険総合データベース）による各年度の値です。本節第7項の北海道「介護保険事業所一覧」（令和8年6月30日現在）とは出典と時点が異なるため、事業所数が一致しな</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
@@ -1710,11 +1710,11 @@
         <v>18</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>493</v>
+        <v>355</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の25箇所の運営主体は、住民団体17・社会福祉協議会6・介護関係施設事業所2で、住民個人が運営する通いの場は0箇所です。住民個人による運営は全国19.2％・北海道28.8％（令和2年度）あり</t>
+          <t>出典：北海道保健福祉部の各名簿（令和8年6月30日〜7月1日現在）、介護老人保健施設及び認知症対応型共同生活介護の一部は居所変更実態調査（令和7年4月1日現在）及び介護サービス情報公表システムの個別公</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
@@ -1724,11 +1724,11 @@
         <v>19</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>522</v>
+        <v>485</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>総給付費は令和6年度96.3％、令和7年度97.8％で、いずれも計画の範囲内です。内訳では、施設サービスが計画を上回る一方、居住系サービスが2か年とも10ポイント以上下回っています。居住系の内訳は、特</t>
+          <t>第9期は5基本目標19施策を掲げましたが、計画全体の代表KPIは4項目です。施策体系の幅に対し成果指標の対象範囲が狭く、相談、医療介護連携、認知症、家族介護、住まい、供給、人材、質、BCP、財政の成果</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
@@ -1738,11 +1738,11 @@
         <v>20</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>530</v>
+        <v>502</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>このほか、第9期計画で計画値を0としながら実績のあるサービスが2つあります。認知症対応型通所介護は令和6年度・令和7年度とも延べ12人・約124万円、介護療養型医療施設は令和6年度に延べ1人・325,</t>
+          <t>令和6年度の25箇所の運営主体は、住民団体17・社会福祉協議会6・介護関係施設事業所2で、住民個人が運営する通いの場は0箇所です。住民個人による運営は全国19.2％・北海道28.8％（令和2年度）あり</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
@@ -1752,11 +1752,11 @@
         <v>21</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>614</v>
+        <v>533</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>総給付費は令和6年度96.3％、令和7年度97.8％で、いずれも計画の範囲内です。内訳では、施設サービスが計画を上回る一方、居住系サービスが2か年とも10ポイント以上下回っています。居住系の内訳は、特</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
@@ -1766,11 +1766,11 @@
         <v>22</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>618</v>
+        <v>541</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>認知症施策については、交付金評価の支援Ⅱが36.3点（全国54.5点の66.6％）で、「認知症地域支援推進員の業務の状況」が全国の33.9％、「認知症サポーター数」が41.7％、「認知症サポーターステ</t>
+          <t>このほか、第9期計画で計画値を0としながら実績のあるサービスが2つあります。認知症対応型通所介護は令和6年度・令和7年度とも延べ12人・約124万円、介護療養型医療施設は令和6年度に延べ1人・325,</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr"/>
@@ -1780,11 +1780,11 @@
         <v>23</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>認知症初期集中支援推進事業は、構成3町がそれぞれ担当チームを設置していますが、実施の状況は町により異なります。令和7年度は、東川町が町立診療所の医師を専門医としてチーム員会議を1回開催した一方、美瑛町</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr"/>
@@ -1794,11 +1794,11 @@
         <v>24</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>621</v>
+        <v>631</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>一方、リハビリテーションの提供体制は当区域の強みです。理学療法士は全国の1.67倍、言語聴覚士は2.41倍が配置され、リハビリテーションマネジメント加算Ⅱ以上の算定は全国の2.66倍、認知症短期集中リ</t>
+          <t>認知症施策については、交付金評価の支援Ⅱが36.3点（全国54.5点の66.6％）で、「認知症地域支援推進員の業務の状況」が全国の33.9％、「認知症サポーター数」が41.7％、「認知症サポーターステ</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr"/>
@@ -1808,11 +1808,11 @@
         <v>25</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>認知症施策について、認知症地域支援推進員の業務内容を明確化し、サポーター養成とステップアップ講座を計画的に実施します。本項は介護保険法第117条第3項による認知症である被保険者の地域における日常生活の</t>
+          <t>認知症初期集中支援推進事業は、構成3町がそれぞれ担当チームを設置していますが、実施の状況は町により異なります。令和7年度は、東川町が町立診療所の医師を専門医としてチーム員会議を1回開催した一方、美瑛町</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr"/>
@@ -1822,11 +1822,11 @@
         <v>26</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>認知症初期集中支援推進事業について、専門医の確保を含む担当チームの体制を3町及び広域連合で確かめ、休止している町の再開の見通しを整理します。あわせて、対応件数と会議の開催回数を町ごとに同じ様式で記録し</t>
+          <t>一方、リハビリテーションの提供体制は当区域の強みです。理学療法士は全国の1.67倍、言語聴覚士は2.41倍が配置され、リハビリテーションマネジメント加算Ⅱ以上の算定は全国の2.66倍、認知症短期集中リ</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr"/>
@@ -1836,11 +1836,11 @@
         <v>27</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>認知症の通所・居住の受け皿が減少していることを踏まえ、既存の小規模多機能型居宅介護（5事業所・全国比4.00倍）との役割分担を検討します。</t>
+          <t>認知症施策について、認知症地域支援推進員の業務内容を明確化し、サポーター養成とステップアップ講座を計画的に実施します。本項は介護保険法第117条第3項による認知症である被保険者の地域における日常生活の</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr"/>
@@ -1850,11 +1850,11 @@
         <v>28</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の定員は縮小しています。介護老人福祉施設の定員は平成29年度234人から令和2年度以降160人へ31.6％減少し、要支援・要介護者1人当たりでは平成30年度0.126人から令和7年度0.0</t>
+          <t>認知症初期集中支援推進事業について、専門医の確保を含む担当チームの体制を3町及び広域連合で確かめ、休止している町の再開の見通しを整理します。あわせて、対応件数と会議の開催回数を町ごとに同じ様式で記録し</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr"/>
@@ -1864,11 +1864,11 @@
         <v>29</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>723</v>
+        <v>645</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護被保険者証の電子資格確認が導入され、要介護認定等の申請の代行を行うことができる者に認知症対応型共同生活介護事業者等が追加されます（第</t>
+          <t>認知症の通所・居住の受け皿が減少していることを踏まえ、既存の小規模多機能型居宅介護（5事業所・全国比4.00倍）との役割分担を検討します。</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr"/>
@@ -1878,11 +1878,11 @@
         <v>30</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>763</v>
+        <v>648</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr"/>
@@ -1892,11 +1892,11 @@
         <v>31</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>771</v>
+        <v>654</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>注）1人1月当たりの回（日）数は、要支援と要介護に分けて置いています。上表は介護給付（要介護1から要介護5まで）の分です。居宅療養管理指導、福祉用具貸与、特定福祉用具購入、住宅改修、小規模多機能型居宅</t>
+          <t>施設・居住系の定員は縮小しています。介護老人福祉施設の定員は平成29年度234人から令和2年度以降160人へ31.6％減少し、要支援・要介護者1人当たりでは平成30年度0.126人から令和7年度0.0</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr"/>
@@ -1906,11 +1906,11 @@
         <v>32</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>781</v>
+        <v>738</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>注）「―」は令和7年度に要支援1・2の利用がないもの（介護予防訪問入浴介護・介護予防認知症対応型通所介護）及び月単位の包括報酬により回数の計上がないもの（介護予防通所リハビリテーション）です。介護予防</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護被保険者証の電子資格確認が導入され、要介護認定等の申請の代行を行うことができる者に認知症対応型共同生活介護事業者等が追加されます（第</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr"/>
@@ -1920,11 +1920,11 @@
         <v>33</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>【認知症総合支援事業の実施状況】</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr"/>
@@ -1934,11 +1934,11 @@
         <v>34</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>801</v>
+        <v>788</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業は包括的支援事業（社会保障充実分）として実施しています。事業ごとの利用者実人数及び事業費を把握できていないため量の見込みは掲げられません。構成3町の実施状況は次のとおりです。</t>
+          <t>注）1人1月当たりの回（日）数は、要支援と要介護に分けて置いています。上表は介護給付（要介護1から要介護5まで）の分です。居宅療養管理指導、福祉用具貸与、特定福祉用具購入、住宅改修、小規模多機能型居宅</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr"/>
@@ -1948,11 +1948,11 @@
         <v>35</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではあり</t>
+          <t>注）「―」は令和7年度に要支援1・2の利用がないもの（介護予防訪問入浴介護・介護予防認知症対応型通所介護）及び月単位の包括報酬により回数の計上がないもの（介護予防通所リハビリテーション）です。介護予防</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr"/>
@@ -1962,11 +1962,11 @@
         <v>36</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行いま</t>
+          <t>【認知症総合支援事業の実施状況】</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr"/>
@@ -1976,11 +1976,11 @@
         <v>37</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>831</v>
+        <v>818</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
+          <t>認知症総合支援事業は包括的支援事業（社会保障充実分）として実施しています。事業ごとの利用者実人数及び事業費を把握できていないため量の見込みは掲げられません。構成3町の実施状況は次のとおりです。</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr"/>
@@ -1990,11 +1990,11 @@
         <v>38</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>836</v>
+        <v>820</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
+          <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではあり</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr"/>
@@ -2004,11 +2004,11 @@
         <v>39</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行いま</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr"/>
@@ -2018,11 +2018,11 @@
         <v>40</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>917</v>
+        <v>848</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増</t>
+          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr"/>
@@ -2032,17 +2032,74 @@
         <v>41</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>966</v>
+        <v>853</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
+          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>857</v>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr"/>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>936</v>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr"/>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>937</v>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr"/>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>986</v>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
           <t>本計画は介護保険法に基づく広域連合の介護保険事業計画であり、構成3町の高齢者福祉計画とは分離して策定します。一方、介護予防、生活支援、認知症、家族介護、医療・介護連携等は相互に影響するため、次の役割分</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr"/>
-    </row>
-    <row r="56" ht="34" customHeight="1">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60" ht="34" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>注）段落の番号は素案の先頭からの通し番号です。素案を改訂すると番号は動きます。本表は素案の実物（docx）から数えているため、素案を改めれば本表も追随します。</t>
         </is>
@@ -2051,9 +2108,9 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A56:D56"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A60:D60"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4487,7 +4544,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（1001段落）から数えた</t>
+          <t>素案の実物（1024段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -4517,7 +4574,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>41段落</t>
+          <t>45段落</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1640,7 +1640,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>17</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>18</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>19</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>20</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>21</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>22</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>23</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>24</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>25</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>26</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>27</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>28</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>29</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>30</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>31</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>32</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>33</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>34</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>36</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>37</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>38</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>39</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>40</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>41</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>42</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>43</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>45</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（1024段落）から数えた</t>
+          <t>素案の実物（1027段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1278,7 +1278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>45段落</t>
+          <t>46段落</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援	70</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援	72</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
@@ -1640,7 +1640,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -1682,11 +1682,11 @@
         <v>16</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>認知症施策は、市町村認知症施策推進計画として構成3町が策定します（第1章第2節）。本計画には、介護保険法第117条第3項により認知症である被保険者の支援に関する事項を掲げ、認知症対応型共同生活介護等の</t>
+          <t>注）認定者数は各年10月末現在であり、第2号被保険者を含みます。年度末現在の第1号被保険者の認定者数（第1節2）とは時点及び対象が異なります。自立度Ⅱ以上はⅡa・Ⅱb・Ⅲa・Ⅲb・Ⅳ・Mの合計です。本</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr"/>
@@ -1696,11 +1696,11 @@
         <v>17</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>321</v>
+        <v>240</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>本表は地域包括ケア「見える化」システム（介護保険総合データベース）による各年度の値です。本節第7項の北海道「介護保険事業所一覧」（令和8年6月30日現在）とは出典と時点が異なるため、事業所数が一致しな</t>
+          <t>認知症施策は、市町村認知症施策推進計画として構成3町が策定します（第1章第2節）。本計画には、介護保険法第117条第3項により認知症である被保険者の支援に関する事項を掲げ、認知症対応型共同生活介護等の</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
@@ -1710,11 +1710,11 @@
         <v>18</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>358</v>
+        <v>323</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>出典：北海道保健福祉部の各名簿（令和8年6月30日〜7月1日現在）、介護老人保健施設及び認知症対応型共同生活介護の一部は居所変更実態調査（令和7年4月1日現在）及び介護サービス情報公表システムの個別公</t>
+          <t>本表は地域包括ケア「見える化」システム（介護保険総合データベース）による各年度の値です。本節第7項の北海道「介護保険事業所一覧」（令和8年6月30日現在）とは出典と時点が異なるため、事業所数が一致しな</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
@@ -1724,11 +1724,11 @@
         <v>19</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>488</v>
+        <v>360</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第9期は5基本目標19施策を掲げましたが、計画全体の代表KPIは4項目です。施策体系の幅に対し成果指標の対象範囲が狭く、相談、医療介護連携、認知症、家族介護、住まい、供給、人材、質、BCP、財政の成果</t>
+          <t>出典：北海道保健福祉部の各名簿（令和8年6月30日〜7月1日現在）、介護老人保健施設及び認知症対応型共同生活介護の一部は居所変更実態調査（令和7年4月1日現在）及び介護サービス情報公表システムの個別公</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
@@ -1738,11 +1738,11 @@
         <v>20</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>505</v>
+        <v>490</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の25箇所の運営主体は、住民団体17・社会福祉協議会6・介護関係施設事業所2で、住民個人が運営する通いの場は0箇所です。住民個人による運営は全国19.2％・北海道28.8％（令和2年度）あり</t>
+          <t>第9期は5基本目標19施策を掲げましたが、計画全体の代表KPIは4項目です。施策体系の幅に対し成果指標の対象範囲が狭く、相談、医療介護連携、認知症、家族介護、住まい、供給、人材、質、BCP、財政の成果</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
@@ -1752,11 +1752,11 @@
         <v>21</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>536</v>
+        <v>507</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>総給付費は令和6年度96.3％、令和7年度97.8％で、いずれも計画の範囲内です。内訳では、施設サービスが計画を上回る一方、居住系サービスが2か年とも10ポイント以上下回っています。居住系の内訳は、特</t>
+          <t>令和6年度の25箇所の運営主体は、住民団体17・社会福祉協議会6・介護関係施設事業所2で、住民個人が運営する通いの場は0箇所です。住民個人による運営は全国19.2％・北海道28.8％（令和2年度）あり</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
@@ -1766,11 +1766,11 @@
         <v>22</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>このほか、第9期計画で計画値を0としながら実績のあるサービスが2つあります。認知症対応型通所介護は令和6年度・令和7年度とも延べ12人・約124万円、介護療養型医療施設は令和6年度に延べ1人・325,</t>
+          <t>総給付費は令和6年度96.3％、令和7年度97.8％で、いずれも計画の範囲内です。内訳では、施設サービスが計画を上回る一方、居住系サービスが2か年とも10ポイント以上下回っています。居住系の内訳は、特</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr"/>
@@ -1780,11 +1780,11 @@
         <v>23</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>630</v>
+        <v>546</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>このほか、第9期計画で計画値を0としながら実績のあるサービスが2つあります。認知症対応型通所介護は令和6年度・令和7年度とも延べ12人・約124万円、介護療養型医療施設は令和6年度に延べ1人・325,</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr"/>
@@ -1794,11 +1794,11 @@
         <v>24</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>認知症施策については、交付金評価の支援Ⅱが36.3点（全国54.5点の66.6％）で、「認知症地域支援推進員の業務の状況」が全国の33.9％、「認知症サポーター数」が41.7％、「認知症サポーターステ</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr"/>
@@ -1808,11 +1808,11 @@
         <v>25</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>認知症初期集中支援推進事業は、構成3町がそれぞれ担当チームを設置していますが、実施の状況は町により異なります。令和7年度は、東川町が町立診療所の医師を専門医としてチーム員会議を1回開催した一方、美瑛町</t>
+          <t>認知症施策については、交付金評価の支援Ⅱが36.3点（全国54.5点の66.6％）で、「認知症地域支援推進員の業務の状況」が全国の33.9％、「認知症サポーター数」が41.7％、「認知症サポーターステ</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr"/>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>一方、リハビリテーションの提供体制は当区域の強みです。理学療法士は全国の1.67倍、言語聴覚士は2.41倍が配置され、リハビリテーションマネジメント加算Ⅱ以上の算定は全国の2.66倍、認知症短期集中リ</t>
+          <t>認知症初期集中支援推進事業は、構成3町がそれぞれ担当チームを設置していますが、実施の状況は町により異なります。令和7年度は、東川町が町立診療所の医師を専門医としてチーム員会議を1回開催した一方、美瑛町</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr"/>
@@ -1836,11 +1836,11 @@
         <v>27</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>認知症施策について、認知症地域支援推進員の業務内容を明確化し、サポーター養成とステップアップ講座を計画的に実施します。本項は介護保険法第117条第3項による認知症である被保険者の地域における日常生活の</t>
+          <t>一方、リハビリテーションの提供体制は当区域の強みです。理学療法士は全国の1.67倍、言語聴覚士は2.41倍が配置され、リハビリテーションマネジメント加算Ⅱ以上の算定は全国の2.66倍、認知症短期集中リ</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr"/>
@@ -1850,11 +1850,11 @@
         <v>28</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>認知症初期集中支援推進事業について、専門医の確保を含む担当チームの体制を3町及び広域連合で確かめ、休止している町の再開の見通しを整理します。あわせて、対応件数と会議の開催回数を町ごとに同じ様式で記録し</t>
+          <t>認知症施策について、認知症地域支援推進員の業務内容を明確化し、サポーター養成とステップアップ講座を計画的に実施します。本項は介護保険法第117条第3項による認知症である被保険者の地域における日常生活の</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr"/>
@@ -1864,11 +1864,11 @@
         <v>29</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>認知症の通所・居住の受け皿が減少していることを踏まえ、既存の小規模多機能型居宅介護（5事業所・全国比4.00倍）との役割分担を検討します。</t>
+          <t>認知症初期集中支援推進事業について、専門医の確保を含む担当チームの体制を3町及び広域連合で確かめ、休止している町の再開の見通しを整理します。あわせて、対応件数と会議の開催回数を町ごとに同じ様式で記録し</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr"/>
@@ -1878,11 +1878,11 @@
         <v>30</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及</t>
+          <t>認知症の通所・居住の受け皿が減少していることを踏まえ、既存の小規模多機能型居宅介護（5事業所・全国比4.00倍）との役割分担を検討します。</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr"/>
@@ -1892,11 +1892,11 @@
         <v>31</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の定員は縮小しています。介護老人福祉施設の定員は平成29年度234人から令和2年度以降160人へ31.6％減少し、要支援・要介護者1人当たりでは平成30年度0.126人から令和7年度0.0</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr"/>
@@ -1906,11 +1906,11 @@
         <v>32</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>741</v>
+        <v>659</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護被保険者証の電子資格確認が導入され、要介護認定等の申請の代行を行うことができる者に認知症対応型共同生活介護事業者等が追加されます（第</t>
+          <t>施設・居住系の定員は縮小しています。介護老人福祉施設の定員は平成29年度234人から令和2年度以降160人へ31.6％減少し、要支援・要介護者1人当たりでは平成30年度0.126人から令和7年度0.0</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr"/>
@@ -1920,11 +1920,11 @@
         <v>33</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>783</v>
+        <v>743</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護被保険者証の電子資格確認が導入され、要介護認定等の申請の代行を行うことができる者に認知症対応型共同生活介護事業者等が追加されます（第</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr"/>
@@ -1934,11 +1934,11 @@
         <v>34</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>注）1人1月当たりの回（日）数は、要支援と要介護に分けて置いています。上表は介護給付（要介護1から要介護5まで）の分です。居宅療養管理指導、福祉用具貸与、特定福祉用具購入、住宅改修、小規模多機能型居宅</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr"/>
@@ -1948,11 +1948,11 @@
         <v>35</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>注）「―」は令和7年度に要支援1・2の利用がないもの（介護予防訪問入浴介護・介護予防認知症対応型通所介護）及び月単位の包括報酬により回数の計上がないもの（介護予防通所リハビリテーション）です。介護予防</t>
+          <t>注）1人1月当たりの回（日）数は、要支援と要介護に分けて置いています。上表は介護給付（要介護1から要介護5まで）の分です。居宅療養管理指導、福祉用具貸与、特定福祉用具購入、住宅改修、小規模多機能型居宅</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr"/>
@@ -1962,11 +1962,11 @@
         <v>36</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>820</v>
+        <v>803</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>【認知症総合支援事業の実施状況】</t>
+          <t>注）「―」は令和7年度に要支援1・2の利用がないもの（介護予防訪問入浴介護・介護予防認知症対応型通所介護）及び月単位の包括報酬により回数の計上がないもの（介護予防通所リハビリテーション）です。介護予防</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr"/>
@@ -1976,11 +1976,11 @@
         <v>37</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業は包括的支援事業（社会保障充実分）として実施しています。事業ごとの利用者実人数及び事業費を把握できていないため量の見込みは掲げられません。構成3町の実施状況は次のとおりです。</t>
+          <t>【認知症総合支援事業の実施状況】</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではあり</t>
+          <t>認知症総合支援事業は包括的支援事業（社会保障充実分）として実施しています。事業ごとの利用者実人数及び事業費を把握できていないため量の見込みは掲げられません。構成3町の実施状況は次のとおりです。</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr"/>
@@ -2004,11 +2004,11 @@
         <v>39</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>844</v>
+        <v>825</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行いま</t>
+          <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではあり</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr"/>
@@ -2018,11 +2018,11 @@
         <v>40</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行いま</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr"/>
@@ -2032,11 +2032,11 @@
         <v>41</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
+          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr"/>
@@ -2046,11 +2046,11 @@
         <v>42</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
+          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr"/>
@@ -2060,11 +2060,11 @@
         <v>43</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>939</v>
+        <v>863</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr"/>
@@ -2074,12 +2074,11 @@
         <v>44</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値</t>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr"/>
@@ -2089,17 +2088,32 @@
         <v>45</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>989</v>
+        <v>943</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>992</v>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
           <t>本計画は介護保険法に基づく広域連合の介護保険事業計画であり、構成3町の高齢者福祉計画とは分離して策定します。一方、介護予防、生活支援、認知症、家族介護、医療・介護連携等は相互に影響するため、次の役割分</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr"/>
-    </row>
-    <row r="60" ht="34" customHeight="1">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61" ht="34" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>注）段落の番号は素案の先頭からの通し番号です。素案を改訂すると番号は動きます。本表は素案の実物（docx）から数えているため、素案を改めれば本表も追随します。</t>
         </is>
@@ -2108,9 +2122,9 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A61:D61"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A60:D60"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4544,7 +4558,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（1027段落）から数えた</t>
+          <t>素案の実物（1030段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -4574,7 +4588,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>45段落</t>
+          <t>46段落</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援	72</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援	73</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
@@ -1626,7 +1626,7 @@
         <v>12</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>17</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>18</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>19</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>20</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>21</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>22</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>23</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>24</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>25</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>26</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>27</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>28</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>29</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>30</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>31</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>32</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>33</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>34</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>36</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>37</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>38</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>39</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>40</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>41</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>42</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>43</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>45</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>943</v>
+        <v>950</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>46</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（1030段落）から数えた</t>
+          <t>素案の実物（1038段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援	73</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援	81</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
@@ -1542,7 +1542,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>7</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>8</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>9</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>10</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>12</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>17</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>18</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>19</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>20</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>21</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>22</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>23</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>552</v>
+        <v>565</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>24</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>638</v>
+        <v>651</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>25</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>642</v>
+        <v>655</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>26</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>643</v>
+        <v>656</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>27</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>645</v>
+        <v>658</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>28</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>654</v>
+        <v>667</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>29</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>655</v>
+        <v>668</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>30</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>656</v>
+        <v>669</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>31</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>659</v>
+        <v>672</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>32</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>665</v>
+        <v>678</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
@@ -1920,11 +1920,11 @@
         <v>33</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>750</v>
+        <v>765</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護被保険者証の電子資格確認が導入され、要介護認定等の申請の代行を行うことができる者に認知症対応型共同生活介護事業者等が追加されます（第</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護被保険者証の電子資格確認が導入され、要介護認定等の申請の代行を行うことができる者に特定施設入居者生活介護を行う指定居宅サービス事業者</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr"/>
@@ -1934,7 +1934,7 @@
         <v>34</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>792</v>
+        <v>808</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>800</v>
+        <v>816</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>36</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>810</v>
+        <v>826</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>37</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>829</v>
+        <v>850</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>38</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>830</v>
+        <v>851</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>39</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>832</v>
+        <v>853</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>40</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>854</v>
+        <v>875</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>41</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>861</v>
+        <v>882</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>42</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>866</v>
+        <v>887</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>43</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>870</v>
+        <v>891</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>949</v>
+        <v>971</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>45</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>950</v>
+        <v>972</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>46</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>1000</v>
+        <v>1022</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（1038段落）から数えた</t>
+          <t>素案の実物（1060段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1278,7 +1278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>46段落</t>
+          <t>47段落</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援	81</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援	82</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
@@ -1640,11 +1640,11 @@
         <v>13</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>242</v>
+        <v>161</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>【認知症高齢者の状況】</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものでは</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr"/>
@@ -1654,11 +1654,11 @@
         <v>14</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>認定調査における認知症高齢者の日常生活自立度Ⅱ以上の方は、平成24年10月末1,190人から令和6年10月末1,498人へ308人（25.9％）増えています。一方、認定者に占める割合は65.5％から6</t>
+          <t>【認知症高齢者の状況】</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
@@ -1668,11 +1668,11 @@
         <v>15</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>資料：地域包括ケア「見える化」システム B7系列（認知症高齢者自立度の状況）</t>
+          <t>認定調査における認知症高齢者の日常生活自立度Ⅱ以上の方は、平成24年10月末1,190人から令和6年10月末1,498人へ308人（25.9％）増えています。一方、認定者に占める割合は65.5％から6</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr"/>
@@ -1682,11 +1682,11 @@
         <v>16</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>注）認定者数は各年10月末現在であり、第2号被保険者を含みます。年度末現在の第1号被保険者の認定者数（第1節2）とは時点及び対象が異なります。自立度Ⅱ以上はⅡa・Ⅱb・Ⅲa・Ⅲb・Ⅳ・Mの合計です。本</t>
+          <t>資料：地域包括ケア「見える化」システム B7系列（認知症高齢者自立度の状況）</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr"/>
@@ -1696,11 +1696,11 @@
         <v>17</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>認知症施策は、市町村認知症施策推進計画として構成3町が策定します（第1章第2節）。本計画には、介護保険法第117条第3項により認知症である被保険者の支援に関する事項を掲げ、認知症対応型共同生活介護等の</t>
+          <t>注）認定者数は各年10月末現在であり、第2号被保険者を含みます。年度末現在の第1号被保険者の認定者数（第1節2）とは時点及び対象が異なります。自立度Ⅱ以上はⅡa・Ⅱb・Ⅲa・Ⅲb・Ⅳ・Mの合計です。本</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
@@ -1710,11 +1710,11 @@
         <v>18</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>330</v>
+        <v>247</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>本表は地域包括ケア「見える化」システム（介護保険総合データベース）による各年度の値です。本節第7項の北海道「介護保険事業所一覧」（令和8年6月30日現在）とは出典と時点が異なるため、事業所数が一致しな</t>
+          <t>認知症施策は、市町村認知症施策推進計画として構成3町が策定します（第1章第2節）。本計画には、介護保険法第117条第3項により認知症である被保険者の支援に関する事項を掲げ、認知症対応型共同生活介護等の</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
@@ -1724,11 +1724,11 @@
         <v>19</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>367</v>
+        <v>330</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>出典：北海道保健福祉部の各名簿（令和8年6月30日〜7月1日現在）、介護老人保健施設及び認知症対応型共同生活介護の一部は居所変更実態調査（令和7年4月1日現在）及び介護サービス情報公表システムの個別公</t>
+          <t>本表は地域包括ケア「見える化」システム（介護保険総合データベース）による各年度の値です。本節第7項の北海道「介護保険事業所一覧」（令和8年6月30日現在）とは出典と時点が異なるため、事業所数が一致しな</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
@@ -1738,11 +1738,11 @@
         <v>20</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>509</v>
+        <v>367</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第9期は5基本目標19施策を掲げましたが、計画全体の代表KPIは4項目です。施策体系の幅に対し成果指標の対象範囲が狭く、相談、医療介護連携、認知症、家族介護、住まい、供給、人材、質、BCP、財政の成果</t>
+          <t>出典：北海道保健福祉部の各名簿（令和8年6月30日〜7月1日現在）、介護老人保健施設及び認知症対応型共同生活介護の一部は居所変更実態調査（令和7年4月1日現在）及び介護サービス情報公表システムの個別公</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
@@ -1752,11 +1752,11 @@
         <v>21</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の25箇所の運営主体は、住民団体17・社会福祉協議会6・介護関係施設事業所2で、住民個人が運営する通いの場は0箇所です。住民個人による運営は全国19.2％・北海道28.8％（令和2年度）あり</t>
+          <t>第9期は5基本目標19施策を掲げましたが、計画全体の代表KPIは4項目です。施策体系の幅に対し成果指標の対象範囲が狭く、相談、医療介護連携、認知症、家族介護、住まい、供給、人材、質、BCP、財政の成果</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
@@ -1766,11 +1766,11 @@
         <v>22</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>557</v>
+        <v>525</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>総給付費は令和6年度96.3％、令和7年度97.8％で、いずれも計画の範囲内です。内訳では、施設サービスが計画を上回る一方、居住系サービスが2か年とも10ポイント以上下回っています。居住系の内訳は、特</t>
+          <t>令和6年度の25箇所の運営主体は、住民団体17・社会福祉協議会6・介護関係施設事業所2で、住民個人が運営する通いの場は0箇所です。住民個人による運営は全国19.2％・北海道28.8％（令和2年度）あり</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr"/>
@@ -1780,11 +1780,11 @@
         <v>23</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>このほか、第9期計画で計画値を0としながら実績のあるサービスが2つあります。認知症対応型通所介護は令和6年度・令和7年度とも延べ12人・約124万円、介護療養型医療施設は令和6年度に延べ1人・325,</t>
+          <t>総給付費は令和6年度96.3％、令和7年度97.8％で、いずれも計画の範囲内です。内訳では、施設サービスが計画を上回る一方、居住系サービスが2か年とも10ポイント以上下回っています。居住系の内訳は、特</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr"/>
@@ -1794,11 +1794,11 @@
         <v>24</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>651</v>
+        <v>564</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>このほか、第9期計画で計画値を0としながら実績のあるサービスが2つあります。認知症対応型通所介護は令和6年度・令和7年度とも延べ12人・約124万円、介護療養型医療施設は令和6年度に延べ1人・325,</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr"/>
@@ -1808,11 +1808,11 @@
         <v>25</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>認知症施策については、交付金評価の支援Ⅱが36.3点（全国54.5点の66.6％）で、「認知症地域支援推進員の業務の状況」が全国の33.9％、「認知症サポーター数」が41.7％、「認知症サポーターステ</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr"/>
@@ -1822,11 +1822,11 @@
         <v>26</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>認知症初期集中支援推進事業は、構成3町がそれぞれ担当チームを設置していますが、実施の状況は町により異なります。令和7年度は、東川町が町立診療所の医師を専門医としてチーム員会議を1回開催した一方、美瑛町</t>
+          <t>認知症施策については、交付金評価の支援Ⅱが36.3点（全国54.5点の66.6％）で、「認知症地域支援推進員の業務の状況」が全国の33.9％、「認知症サポーター数」が41.7％、「認知症サポーターステ</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr"/>
@@ -1836,11 +1836,11 @@
         <v>27</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>一方、リハビリテーションの提供体制は当区域の強みです。理学療法士は全国の1.67倍、言語聴覚士は2.41倍が配置され、リハビリテーションマネジメント加算Ⅱ以上の算定は全国の2.66倍、認知症短期集中リ</t>
+          <t>認知症初期集中支援推進事業は、構成3町がそれぞれ担当チームを設置していますが、実施の状況は町により異なります。令和7年度は、東川町が町立診療所の医師を専門医としてチーム員会議を1回開催した一方、美瑛町</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr"/>
@@ -1850,11 +1850,11 @@
         <v>28</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>認知症施策について、認知症地域支援推進員の業務内容を明確化し、サポーター養成とステップアップ講座を計画的に実施します。本項は介護保険法第117条第3項による認知症である被保険者の地域における日常生活の</t>
+          <t>一方、リハビリテーションの提供体制は当区域の強みです。理学療法士は全国の1.67倍、言語聴覚士は2.41倍が配置され、リハビリテーションマネジメント加算Ⅱ以上の算定は全国の2.66倍、認知症短期集中リ</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr"/>
@@ -1864,11 +1864,11 @@
         <v>29</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>認知症初期集中支援推進事業について、専門医の確保を含む担当チームの体制を3町及び広域連合で確かめ、休止している町の再開の見通しを整理します。あわせて、対応件数と会議の開催回数を町ごとに同じ様式で記録し</t>
+          <t>認知症施策について、認知症地域支援推進員の業務内容を明確化し、サポーター養成とステップアップ講座を計画的に実施します。本項は介護保険法第117条第3項による認知症である被保険者の地域における日常生活の</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr"/>
@@ -1878,11 +1878,11 @@
         <v>30</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>認知症の通所・居住の受け皿が減少していることを踏まえ、既存の小規模多機能型居宅介護（5事業所・全国比4.00倍）との役割分担を検討します。</t>
+          <t>認知症初期集中支援推進事業について、専門医の確保を含む担当チームの体制を3町及び広域連合で確かめ、休止している町の再開の見通しを整理します。あわせて、対応件数と会議の開催回数を町ごとに同じ様式で記録し</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr"/>
@@ -1892,11 +1892,11 @@
         <v>31</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及</t>
+          <t>認知症の通所・居住の受け皿が減少していることを踏まえ、既存の小規模多機能型居宅介護（5事業所・全国比4.00倍）との役割分担を検討します。</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr"/>
@@ -1906,11 +1906,11 @@
         <v>32</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の定員は縮小しています。介護老人福祉施設の定員は平成29年度234人から令和2年度以降160人へ31.6％減少し、要支援・要介護者1人当たりでは平成30年度0.126人から令和7年度0.0</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr"/>
@@ -1920,11 +1920,11 @@
         <v>33</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>765</v>
+        <v>677</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護被保険者証の電子資格確認が導入され、要介護認定等の申請の代行を行うことができる者に特定施設入居者生活介護を行う指定居宅サービス事業者</t>
+          <t>施設・居住系の定員は縮小しています。介護老人福祉施設の定員は平成29年度234人から令和2年度以降160人へ31.6％減少し、要支援・要介護者1人当たりでは平成30年度0.126人から令和7年度0.0</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr"/>
@@ -1934,11 +1934,11 @@
         <v>34</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>808</v>
+        <v>764</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護被保険者証の電子資格確認が導入され、要介護認定等の申請の代行を行うことができる者に特定施設入居者生活介護を行う指定居宅サービス事業者</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr"/>
@@ -1948,11 +1948,11 @@
         <v>35</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>816</v>
+        <v>807</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>注）1人1月当たりの回（日）数は、要支援と要介護に分けて置いています。上表は介護給付（要介護1から要介護5まで）の分です。居宅療養管理指導、福祉用具貸与、特定福祉用具購入、住宅改修、小規模多機能型居宅</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr"/>
@@ -1962,11 +1962,11 @@
         <v>36</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>826</v>
+        <v>815</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>注）「―」は令和7年度に要支援1・2の利用がないもの（介護予防訪問入浴介護・介護予防認知症対応型通所介護）及び月単位の包括報酬により回数の計上がないもの（介護予防通所リハビリテーション）です。介護予防</t>
+          <t>注）1人1月当たりの回（日）数は、要支援と要介護に分けて置いています。上表は介護給付（要介護1から要介護5まで）の分です。居宅療養管理指導、福祉用具貸与、特定福祉用具購入、住宅改修、小規模多機能型居宅</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr"/>
@@ -1976,11 +1976,11 @@
         <v>37</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>850</v>
+        <v>825</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>【認知症総合支援事業の実施状況】</t>
+          <t>注）「―」は令和7年度に要支援1・2の利用がないもの（介護予防訪問入浴介護・介護予防認知症対応型通所介護）及び月単位の包括報酬により回数の計上がないもの（介護予防通所リハビリテーション）です。介護予防</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr"/>
@@ -1990,11 +1990,11 @@
         <v>38</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業は包括的支援事業（社会保障充実分）として実施しています。事業ごとの利用者実人数及び事業費を把握できていないため量の見込みは掲げられません。構成3町の実施状況は次のとおりです。</t>
+          <t>【認知症総合支援事業の実施状況】</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr"/>
@@ -2004,11 +2004,11 @@
         <v>39</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではあり</t>
+          <t>認知症総合支援事業は包括的支援事業（社会保障充実分）として実施しています。事業ごとの利用者実人数及び事業費を把握できていないため量の見込みは掲げられません。構成3町の実施状況は次のとおりです。</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr"/>
@@ -2018,11 +2018,11 @@
         <v>40</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>875</v>
+        <v>852</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行いま</t>
+          <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではあり</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr"/>
@@ -2032,11 +2032,11 @@
         <v>41</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行いま</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr"/>
@@ -2046,11 +2046,11 @@
         <v>42</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
+          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr"/>
@@ -2060,11 +2060,11 @@
         <v>43</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
+          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr"/>
@@ -2074,11 +2074,11 @@
         <v>44</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>971</v>
+        <v>890</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr"/>
@@ -2088,12 +2088,11 @@
         <v>45</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値</t>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr"/>
@@ -2103,17 +2102,32 @@
         <v>46</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>1022</v>
+        <v>971</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>1021</v>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
           <t>本計画は介護保険法に基づく広域連合の介護保険事業計画であり、構成3町の高齢者福祉計画とは分離して策定します。一方、介護予防、生活支援、認知症、家族介護、医療・介護連携等は相互に影響するため、次の役割分</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr"/>
-    </row>
-    <row r="61" ht="34" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62" ht="34" customHeight="1">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>注）段落の番号は素案の先頭からの通し番号です。素案を改訂すると番号は動きます。本表は素案の実物（docx）から数えているため、素案を改めれば本表も追随します。</t>
         </is>
@@ -2122,9 +2136,9 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A61:D61"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4558,7 +4572,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（1060段落）から数えた</t>
+          <t>素案の実物（1059段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -4588,7 +4602,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>46段落</t>
+          <t>47段落</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1278,7 +1278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>47段落</t>
+          <t>48段落</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -1570,7 +1570,7 @@
         <v>8</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>9</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>10</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>12</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>17</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>18</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>19</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>20</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>21</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>22</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>23</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>24</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>25</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>26</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>27</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>28</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>29</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>30</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>31</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>32</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>33</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>34</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>36</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>37</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>38</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>39</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>40</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>41</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>42</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>43</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
@@ -2088,11 +2088,11 @@
         <v>45</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>970</v>
+        <v>895</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増</t>
+          <t>介護保険法第117条第2項第1号により本計画が定める必要利用定員総数は、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の3つのサービスです。介護</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr"/>
@@ -2102,12 +2102,11 @@
         <v>46</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値</t>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr"/>
@@ -2117,17 +2116,32 @@
         <v>47</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>1021</v>
+        <v>974</v>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>1024</v>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
           <t>本計画は介護保険法に基づく広域連合の介護保険事業計画であり、構成3町の高齢者福祉計画とは分離して策定します。一方、介護予防、生活支援、認知症、家族介護、医療・介護連携等は相互に影響するため、次の役割分</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr"/>
-    </row>
-    <row r="62" ht="34" customHeight="1">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr"/>
+    </row>
+    <row r="63" ht="34" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>注）段落の番号は素案の先頭からの通し番号です。素案を改訂すると番号は動きます。本表は素案の実物（docx）から数えているため、素案を改めれば本表も追随します。</t>
         </is>
@@ -2138,7 +2152,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A63:D63"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4572,7 +4586,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（1059段落）から数えた</t>
+          <t>素案の実物（1062段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -4602,7 +4616,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>47段落</t>
+          <t>48段落</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1278,7 +1278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>48段落</t>
+          <t>49段落</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援	82</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援	74</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況</t>
+          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。都道府県認知症施策推進計画については、北海道の第10期高齢者保健福祉計画</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
@@ -1612,7 +1612,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>12</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>17</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>18</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         <v>19</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>20</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -1752,11 +1752,11 @@
         <v>21</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>510</v>
+        <v>409</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第9期は5基本目標19施策を掲げましたが、計画全体の代表KPIは4項目です。施策体系の幅に対し成果指標の対象範囲が狭く、相談、医療介護連携、認知症、家族介護、住まい、供給、人材、質、BCP、財政の成果</t>
+          <t>定員及び従事者数は介護サービス情報公表システム（各年9月時点）、利用者数は介護保険総合データベース（各年9月サービス分）によります。対象は最新年度の9月サービス分の算定実績のある事業所に限られ、介護予</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
@@ -1766,11 +1766,11 @@
         <v>22</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の25箇所の運営主体は、住民団体17・社会福祉協議会6・介護関係施設事業所2で、住民個人が運営する通いの場は0箇所です。住民個人による運営は全国19.2％・北海道28.8％（令和2年度）あり</t>
+          <t>第9期は5基本目標19施策を掲げましたが、計画全体の代表KPIは4項目です。施策体系の幅に対し成果指標の対象範囲が狭く、相談、医療介護連携、認知症、家族介護、住まい、供給、人材、質、BCP、財政の成果</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr"/>
@@ -1780,11 +1780,11 @@
         <v>23</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>総給付費は令和6年度96.3％、令和7年度97.8％で、いずれも計画の範囲内です。内訳では、施設サービスが計画を上回る一方、居住系サービスが2か年とも10ポイント以上下回っています。居住系の内訳は、特</t>
+          <t>令和6年度の25箇所の運営主体は、住民団体17・社会福祉協議会6・介護関係施設事業所2で、住民個人が運営する通いの場は0箇所です。住民個人による運営は全国19.2％・北海道28.8％（令和2年度）あり</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr"/>
@@ -1794,11 +1794,11 @@
         <v>24</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>このほか、第9期計画で計画値を0としながら実績のあるサービスが2つあります。認知症対応型通所介護は令和6年度・令和7年度とも延べ12人・約124万円、介護療養型医療施設は令和6年度に延べ1人・325,</t>
+          <t>総給付費は令和6年度96.3％、令和7年度97.8％で、いずれも計画の範囲内です。内訳では、施設サービスが計画を上回る一方、居住系サービスが2か年とも10ポイント以上下回っています。居住系の内訳は、特</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr"/>
@@ -1808,11 +1808,11 @@
         <v>25</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>652</v>
+        <v>581</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>このほか、第9期計画で計画値を0としながら実績のあるサービスが2つあります。認知症対応型通所介護は令和6年度・令和7年度とも延べ12人・約124万円、介護療養型医療施設は令和6年度に延べ1人・325,</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr"/>
@@ -1822,11 +1822,11 @@
         <v>26</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>認知症施策については、交付金評価の支援Ⅱが36.3点（全国54.5点の66.6％）で、「認知症地域支援推進員の業務の状況」が全国の33.9％、「認知症サポーター数」が41.7％、「認知症サポーターステ</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr"/>
@@ -1836,11 +1836,11 @@
         <v>27</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>657</v>
+        <v>672</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>認知症初期集中支援推進事業は、構成3町がそれぞれ担当チームを設置していますが、実施の状況は町により異なります。令和7年度は、東川町が町立診療所の医師を専門医としてチーム員会議を1回開催した一方、美瑛町</t>
+          <t>認知症施策については、交付金評価の支援Ⅱが36.3点（全国54.5点の66.6％）で、「認知症地域支援推進員の業務の状況」が全国の33.9％、「認知症サポーター数」が41.7％、「認知症サポーターステ</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr"/>
@@ -1850,11 +1850,11 @@
         <v>28</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>659</v>
+        <v>673</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>一方、リハビリテーションの提供体制は当区域の強みです。理学療法士は全国の1.67倍、言語聴覚士は2.41倍が配置され、リハビリテーションマネジメント加算Ⅱ以上の算定は全国の2.66倍、認知症短期集中リ</t>
+          <t>認知症初期集中支援推進事業は、構成3町がそれぞれ担当チームを設置していますが、実施の状況は町により異なります。令和7年度は、東川町が町立診療所の医師を専門医としてチーム員会議を1回開催した一方、美瑛町</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr"/>
@@ -1864,11 +1864,11 @@
         <v>29</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>認知症施策について、認知症地域支援推進員の業務内容を明確化し、サポーター養成とステップアップ講座を計画的に実施します。本項は介護保険法第117条第3項による認知症である被保険者の地域における日常生活の</t>
+          <t>一方、リハビリテーションの提供体制は当区域の強みです。理学療法士は全国の1.67倍、言語聴覚士は2.41倍が配置され、リハビリテーションマネジメント加算Ⅱ以上の算定は全国の2.66倍、認知症短期集中リ</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr"/>
@@ -1878,11 +1878,11 @@
         <v>30</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>669</v>
+        <v>684</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>認知症初期集中支援推進事業について、専門医の確保を含む担当チームの体制を3町及び広域連合で確かめ、休止している町の再開の見通しを整理します。あわせて、対応件数と会議の開催回数を町ごとに同じ様式で記録し</t>
+          <t>認知症施策について、認知症地域支援推進員の業務内容を明確化し、サポーター養成とステップアップ講座を計画的に実施します。本項は介護保険法第117条第3項による認知症である被保険者の地域における日常生活の</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr"/>
@@ -1892,11 +1892,11 @@
         <v>31</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>670</v>
+        <v>685</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>認知症の通所・居住の受け皿が減少していることを踏まえ、既存の小規模多機能型居宅介護（5事業所・全国比4.00倍）との役割分担を検討します。</t>
+          <t>認知症初期集中支援推進事業について、専門医の確保を含む担当チームの体制を3町及び広域連合で確かめ、休止している町の再開の見通しを整理します。あわせて、対応件数と会議の開催回数を町ごとに同じ様式で記録し</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr"/>
@@ -1906,11 +1906,11 @@
         <v>32</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>673</v>
+        <v>686</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及</t>
+          <t>認知症の通所・居住の受け皿が減少していることを踏まえ、既存の小規模多機能型居宅介護（5事業所・全国比4.00倍）との役割分担を検討します。</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr"/>
@@ -1920,11 +1920,11 @@
         <v>33</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>679</v>
+        <v>689</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の定員は縮小しています。介護老人福祉施設の定員は平成29年度234人から令和2年度以降160人へ31.6％減少し、要支援・要介護者1人当たりでは平成30年度0.126人から令和7年度0.0</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr"/>
@@ -1934,11 +1934,11 @@
         <v>34</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>766</v>
+        <v>695</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護被保険者証の電子資格確認が導入され、要介護認定等の申請の代行を行うことができる者に特定施設入居者生活介護を行う指定居宅サービス事業者</t>
+          <t>施設・居住系の定員は縮小しています。介護老人福祉施設の定員は平成29年度234人から令和2年度以降160人へ31.6％減少し、要支援・要介護者1人当たりでは平成30年度0.126人から令和7年度0.0</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr"/>
@@ -1948,11 +1948,11 @@
         <v>35</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>809</v>
+        <v>782</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護被保険者証の電子資格確認が導入され、要介護認定等の申請の代行を行うことができる者に特定施設入居者生活介護を行う指定居宅サービス事業者</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr"/>
@@ -1962,11 +1962,11 @@
         <v>36</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>注）1人1月当たりの回（日）数は、要支援と要介護に分けて置いています。上表は介護給付（要介護1から要介護5まで）の分です。居宅療養管理指導、福祉用具貸与、特定福祉用具購入、住宅改修、小規模多機能型居宅</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr"/>
@@ -1976,11 +1976,11 @@
         <v>37</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>注）「―」は令和7年度に要支援1・2の利用がないもの（介護予防訪問入浴介護・介護予防認知症対応型通所介護）及び月単位の包括報酬により回数の計上がないもの（介護予防通所リハビリテーション）です。介護予防</t>
+          <t>注）1人1月当たりの回（日）数は、要支援と要介護に分けて置いています。上表は介護給付（要介護1から要介護5まで）の分です。居宅療養管理指導、福祉用具貸与、特定福祉用具購入、住宅改修、小規模多機能型居宅</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr"/>
@@ -1990,11 +1990,11 @@
         <v>38</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>【認知症総合支援事業の実施状況】</t>
+          <t>注）「―」は令和7年度に要支援1・2の利用がないもの（介護予防訪問入浴介護・介護予防認知症対応型通所介護）及び月単位の包括報酬により回数の計上がないもの（介護予防通所リハビリテーション）です。介護予防</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr"/>
@@ -2004,11 +2004,11 @@
         <v>39</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>852</v>
+        <v>867</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業は包括的支援事業（社会保障充実分）として実施しています。事業ごとの利用者実人数及び事業費を把握できていないため量の見込みは掲げられません。構成3町の実施状況は次のとおりです。</t>
+          <t>【認知症総合支援事業の実施状況】</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr"/>
@@ -2018,11 +2018,11 @@
         <v>40</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>854</v>
+        <v>868</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではあり</t>
+          <t>認知症総合支援事業は包括的支援事業（社会保障充実分）として実施しています。事業ごとの利用者実人数及び事業費を把握できていないため量の見込みは掲げられません。構成3町の実施状況は次のとおりです。</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr"/>
@@ -2032,11 +2032,11 @@
         <v>41</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行いま</t>
+          <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではあり</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr"/>
@@ -2046,11 +2046,11 @@
         <v>42</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>883</v>
+        <v>893</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行いま</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr"/>
@@ -2060,11 +2060,11 @@
         <v>43</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>888</v>
+        <v>900</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
+          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr"/>
@@ -2074,11 +2074,11 @@
         <v>44</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>892</v>
+        <v>905</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
+          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr"/>
@@ -2088,11 +2088,11 @@
         <v>45</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>895</v>
+        <v>909</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項第1号により本計画が定める必要利用定員総数は、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の3つのサービスです。介護</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr"/>
@@ -2102,11 +2102,11 @@
         <v>46</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>973</v>
+        <v>912</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増</t>
+          <t>介護保険法第117条第2項第1号により本計画が定める必要利用定員総数は、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の3つのサービスです。介護</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr"/>
@@ -2116,12 +2116,11 @@
         <v>47</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>974</v>
+        <v>994</v>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値</t>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr"/>
@@ -2131,17 +2130,32 @@
         <v>48</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>1024</v>
+        <v>995</v>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr"/>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>1045</v>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
           <t>本計画は介護保険法に基づく広域連合の介護保険事業計画であり、構成3町の高齢者福祉計画とは分離して策定します。一方、介護予防、生活支援、認知症、家族介護、医療・介護連携等は相互に影響するため、次の役割分</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr"/>
-    </row>
-    <row r="63" ht="34" customHeight="1">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr"/>
+    </row>
+    <row r="64" ht="34" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>注）段落の番号は素案の先頭からの通し番号です。素案を改訂すると番号は動きます。本表は素案の実物（docx）から数えているため、素案を改めれば本表も追随します。</t>
         </is>
@@ -2152,7 +2166,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A64:D64"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4586,7 +4600,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（1062段落）から数えた</t>
+          <t>素案の実物（1083段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -4616,7 +4630,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>48段落</t>
+          <t>49段落</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">

--- a/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
+++ b/output/第10期計画_認知症施策推進計画の位置づけと見込量への反映.xlsx
@@ -1278,7 +1278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>49段落</t>
+          <t>55段落</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>5件</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>介護保険法以外の法律が市町村を名宛人として定める計画等についても、市町村認知症施策推進計画と同じ整理により、構成3町がそれぞれ定めます。老人福祉法第20条の8は市町村老人福祉計画を定めるものとし、同計</t>
+          <t>認知症施策推進基本計画（令和6年12月）の重点目標</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
@@ -1542,11 +1542,11 @@
         <v>6</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
+          <t>資料：厚生労働省「認知症施策推進基本計画」（令和6年12月）</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
@@ -1556,11 +1556,11 @@
         <v>7</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は</t>
+          <t>国の認知症施策推進基本計画は、市町村計画に定める内容が介護保険事業計画等の既存の行政計画に定める内容と重複する場合に、これらを一体のものとして策定することは差し支えないものとするなど、必要に応じて柔軟</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr"/>
@@ -1570,11 +1570,11 @@
         <v>8</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>認知症施策推進基本計画（認知症基本法第11条により国が定めるもの）、北海道高齢者保健福祉計画・介護保険事業支援計画、医療計画・地域医療構想、都道府県認知症施策推進計画、地域福祉計画、健康増進計画、障が</t>
+          <t>認知症基本法第13条第2項により、市町村認知症施策推進計画は、市町村地域福祉計画（社会福祉法第107条第1項）、市町村老人福祉計画（老人福祉法第20条の8第1項）、市町村介護保険事業計画（介護保険法第</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr"/>
@@ -1584,11 +1584,11 @@
         <v>9</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画とは別の計画として策定し、介護予防、生活支援、認知症、家族介護、医療・介護連携等は、共通指標と役割分担により接続します。詳細は資料編に示します。構成3町の高齢者福祉計画は老人福</t>
+          <t>介護保険法以外の法律が市町村を名宛人として定める計画等についても、市町村認知症施策推進計画と同じ整理により、構成3町がそれぞれ定めます。老人福祉法第20条の8は市町村老人福祉計画を定めるものとし、同計</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1598,11 +1598,11 @@
         <v>10</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。都道府県認知症施策推進計画については、北海道の第10期高齢者保健福祉計画</t>
+          <t>注）認知症基本法、老人福祉法、成年後見制度の利用の促進に関する法律及び高齢者虐待の防止、高齢者の養護者に対する支援等に関する法律の各条項は、法令の本文により確認したものです。社会福祉法等の一部を改正す</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
@@ -1612,11 +1612,11 @@
         <v>11</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>154</v>
+        <v>74</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施</t>
+          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr"/>
@@ -1626,11 +1626,11 @@
         <v>12</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>156</v>
+        <v>90</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>あわせて、生産性向上の取組に係る委員会の設置についても、経過措置の終了により令和9年4月1日から義務となります。当広域連合において対象となるのは、小規模多機能型居宅介護5事業所、認知症対応型共同生活介</t>
+          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr"/>
@@ -1640,11 +1640,11 @@
         <v>13</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものでは</t>
+          <t>認知症施策推進基本計画（認知症基本法第11条により国が定めるもの）、北海道高齢者保健福祉計画・介護保険事業支援計画、医療計画・地域医療構想、都道府県認知症施策推進計画、地域福祉計画、健康増進計画、障が</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr"/>
@@ -1654,11 +1654,11 @@
         <v>14</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>248</v>
+        <v>128</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>【認知症高齢者の状況】</t>
+          <t>構成3町の高齢者福祉計画とは別の計画として策定し、介護予防、生活支援、認知症、家族介護、医療・介護連携等は、共通指標と役割分担により接続します。詳細は資料編に示します。構成3町の高齢者福祉計画は老人福</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
@@ -1668,11 +1668,11 @@
         <v>15</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>249</v>
+        <v>129</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>認定調査における認知症高齢者の日常生活自立度Ⅱ以上の方は、平成24年10月末1,190人から令和6年10月末1,498人へ308人（25.9％）増えています。一方、認定者に占める割合は65.5％から6</t>
+          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。都道府県認知症施策推進計画については、北海道の第10期高齢者保健福祉計画</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr"/>
@@ -1682,11 +1682,11 @@
         <v>16</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>資料：地域包括ケア「見える化」システム B7系列（認知症高齢者自立度の状況）</t>
+          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr"/>
@@ -1696,11 +1696,11 @@
         <v>17</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>252</v>
+        <v>160</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>注）認定者数は各年10月末現在であり、第2号被保険者を含みます。年度末現在の第1号被保険者の認定者数（第1節2）とは時点及び対象が異なります。自立度Ⅱ以上はⅡa・Ⅱb・Ⅲa・Ⅲb・Ⅳ・Mの合計です。本</t>
+          <t>あわせて、生産性向上の取組に係る委員会の設置についても、経過措置の終了により令和9年4月1日から義務となります。当広域連合において対象となるのは、小規模多機能型居宅介護5事業所、認知症対応型共同生活介</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
@@ -1710,11 +1710,11 @@
         <v>18</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>253</v>
+        <v>171</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>認知症施策は、市町村認知症施策推進計画として構成3町が策定します（第1章第2節）。本計画には、介護保険法第117条第3項により認知症である被保険者の支援に関する事項を掲げ、認知症対応型共同生活介護等の</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものでは</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
@@ -1724,11 +1724,11 @@
         <v>19</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>336</v>
+        <v>252</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>本表は地域包括ケア「見える化」システム（介護保険総合データベース）による各年度の値です。本節第7項の北海道「介護保険事業所一覧」（令和8年6月30日現在）とは出典と時点が異なるため、事業所数が一致しな</t>
+          <t>【認知症高齢者の状況】</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
@@ -1738,11 +1738,11 @@
         <v>20</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>373</v>
+        <v>253</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>出典：北海道保健福祉部の各名簿（令和8年6月30日〜7月1日現在）、介護老人保健施設及び認知症対応型共同生活介護の一部は居所変更実態調査（令和7年4月1日現在）及び介護サービス情報公表システムの個別公</t>
+          <t>認定調査における認知症高齢者の日常生活自立度Ⅱ以上の方は、平成24年10月末1,190人から令和6年10月末1,498人へ308人（25.9％）増えています。一方、認定者に占める割合は65.5％から6</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
@@ -1752,11 +1752,11 @@
         <v>21</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>409</v>
+        <v>255</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>定員及び従事者数は介護サービス情報公表システム（各年9月時点）、利用者数は介護保険総合データベース（各年9月サービス分）によります。対象は最新年度の9月サービス分の算定実績のある事業所に限られ、介護予</t>
+          <t>資料：地域包括ケア「見える化」システム B7系列（認知症高齢者自立度の状況）</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
@@ -1766,11 +1766,11 @@
         <v>22</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>525</v>
+        <v>256</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第9期は5基本目標19施策を掲げましたが、計画全体の代表KPIは4項目です。施策体系の幅に対し成果指標の対象範囲が狭く、相談、医療介護連携、認知症、家族介護、住まい、供給、人材、質、BCP、財政の成果</t>
+          <t>注）認定者数は各年10月末現在であり、第2号被保険者を含みます。年度末現在の第1号被保険者の認定者数（第1節2）とは時点及び対象が異なります。自立度Ⅱ以上はⅡa・Ⅱb・Ⅲa・Ⅲb・Ⅳ・Mの合計です。本</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr"/>
@@ -1780,11 +1780,11 @@
         <v>23</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>542</v>
+        <v>257</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の25箇所の運営主体は、住民団体17・社会福祉協議会6・介護関係施設事業所2で、住民個人が運営する通いの場は0箇所です。住民個人による運営は全国19.2％・北海道28.8％（令和2年度）あり</t>
+          <t>認知症施策は、市町村認知症施策推進計画として構成3町が策定します（第1章第2節）。本計画には、介護保険法第117条第3項により認知症である被保険者の支援に関する事項を掲げ、認知症対応型共同生活介護等の</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr"/>
@@ -1794,11 +1794,11 @@
         <v>24</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>573</v>
+        <v>340</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>総給付費は令和6年度96.3％、令和7年度97.8％で、いずれも計画の範囲内です。内訳では、施設サービスが計画を上回る一方、居住系サービスが2か年とも10ポイント以上下回っています。居住系の内訳は、特</t>
+          <t>本表は地域包括ケア「見える化」システム（介護保険総合データベース）による各年度の値です。本節第7項の北海道「介護保険事業所一覧」（令和8年6月30日現在）とは出典と時点が異なるため、事業所数が一致しな</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr"/>
@@ -1808,11 +1808,11 @@
         <v>25</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>581</v>
+        <v>377</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>このほか、第9期計画で計画値を0としながら実績のあるサービスが2つあります。認知症対応型通所介護は令和6年度・令和7年度とも延べ12人・約124万円、介護療養型医療施設は令和6年度に延べ1人・325,</t>
+          <t>出典：北海道保健福祉部の各名簿（令和8年6月30日〜7月1日現在）、介護老人保健施設及び認知症対応型共同生活介護の一部は居所変更実態調査（令和7年4月1日現在）及び介護サービス情報公表システムの個別公</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr"/>
@@ -1822,11 +1822,11 @@
         <v>26</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>668</v>
+        <v>413</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>定員及び従事者数は介護サービス情報公表システム（各年9月時点）、利用者数は介護保険総合データベース（各年9月サービス分）によります。対象は最新年度の9月サービス分の算定実績のある事業所に限られ、介護予</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr"/>
@@ -1836,11 +1836,11 @@
         <v>27</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>672</v>
+        <v>529</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>認知症施策については、交付金評価の支援Ⅱが36.3点（全国54.5点の66.6％）で、「認知症地域支援推進員の業務の状況」が全国の33.9％、「認知症サポーター数」が41.7％、「認知症サポーターステ</t>
+          <t>第9期は5基本目標19施策を掲げましたが、計画全体の代表KPIは4項目です。施策体系の幅に対し成果指標の対象範囲が狭く、相談、医療介護連携、認知症、家族介護、住まい、供給、人材、質、BCP、財政の成果</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr"/>
@@ -1850,11 +1850,11 @@
         <v>28</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>673</v>
+        <v>546</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>認知症初期集中支援推進事業は、構成3町がそれぞれ担当チームを設置していますが、実施の状況は町により異なります。令和7年度は、東川町が町立診療所の医師を専門医としてチーム員会議を1回開催した一方、美瑛町</t>
+          <t>令和6年度の25箇所の運営主体は、住民団体17・社会福祉協議会6・介護関係施設事業所2で、住民個人が運営する通いの場は0箇所です。住民個人による運営は全国19.2％・北海道28.8％（令和2年度）あり</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr"/>
@@ -1864,11 +1864,11 @@
         <v>29</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>675</v>
+        <v>577</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>一方、リハビリテーションの提供体制は当区域の強みです。理学療法士は全国の1.67倍、言語聴覚士は2.41倍が配置され、リハビリテーションマネジメント加算Ⅱ以上の算定は全国の2.66倍、認知症短期集中リ</t>
+          <t>総給付費は令和6年度96.3％、令和7年度97.8％で、いずれも計画の範囲内です。内訳では、施設サービスが計画を上回る一方、居住系サービスが2か年とも10ポイント以上下回っています。居住系の内訳は、特</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr"/>
@@ -1878,11 +1878,11 @@
         <v>30</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>684</v>
+        <v>585</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>認知症施策について、認知症地域支援推進員の業務内容を明確化し、サポーター養成とステップアップ講座を計画的に実施します。本項は介護保険法第117条第3項による認知症である被保険者の地域における日常生活の</t>
+          <t>このほか、第9期計画で計画値を0としながら実績のあるサービスが2つあります。認知症対応型通所介護は令和6年度・令和7年度とも延べ12人・約124万円、介護療養型医療施設は令和6年度に延べ1人・325,</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr"/>
@@ -1892,11 +1892,11 @@
         <v>31</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>685</v>
+        <v>672</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>認知症初期集中支援推進事業について、専門医の確保を含む担当チームの体制を3町及び広域連合で確かめ、休止している町の再開の見通しを整理します。あわせて、対応件数と会議の開催回数を町ごとに同じ様式で記録し</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr"/>
@@ -1906,11 +1906,11 @@
         <v>32</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>認知症の通所・居住の受け皿が減少していることを踏まえ、既存の小規模多機能型居宅介護（5事業所・全国比4.00倍）との役割分担を検討します。</t>
+          <t>認知症施策については、交付金評価の支援Ⅱが36.3点（全国54.5点の66.6％）で、「認知症地域支援推進員の業務の状況」が全国の33.9％、「認知症サポーター数」が41.7％、「認知症サポーターステ</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr"/>
@@ -1920,11 +1920,11 @@
         <v>33</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及</t>
+          <t>認知症初期集中支援推進事業は、構成3町がそれぞれ担当チームを設置していますが、実施の状況は町により異なります。令和7年度は、東川町が町立診療所の医師を専門医としてチーム員会議を1回開催した一方、美瑛町</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr"/>
@@ -1934,11 +1934,11 @@
         <v>34</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>695</v>
+        <v>679</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の定員は縮小しています。介護老人福祉施設の定員は平成29年度234人から令和2年度以降160人へ31.6％減少し、要支援・要介護者1人当たりでは平成30年度0.126人から令和7年度0.0</t>
+          <t>一方、リハビリテーションの提供体制は当区域の強みです。理学療法士は全国の1.67倍、言語聴覚士は2.41倍が配置され、リハビリテーションマネジメント加算Ⅱ以上の算定は全国の2.66倍、認知症短期集中リ</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr"/>
@@ -1948,11 +1948,11 @@
         <v>35</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>782</v>
+        <v>688</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護被保険者証の電子資格確認が導入され、要介護認定等の申請の代行を行うことができる者に特定施設入居者生活介護を行う指定居宅サービス事業者</t>
+          <t>認知症施策について、認知症地域支援推進員の業務内容を明確化し、サポーター養成とステップアップ講座を計画的に実施します。本項は介護保険法第117条第3項による認知症である被保険者の地域における日常生活の</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr"/>
@@ -1962,11 +1962,11 @@
         <v>36</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>825</v>
+        <v>689</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］</t>
+          <t>国の認知症施策推進基本計画（令和6年12月3日 閣議決定）が掲げる重点目標4件との対応を確かめ、同計画が示す指標の3つの観点（プロセス指標・アウトプット指標・アウトカム指標）に沿って本計画の指標を整理</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr"/>
@@ -1976,11 +1976,11 @@
         <v>37</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>833</v>
+        <v>690</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>注）1人1月当たりの回（日）数は、要支援と要介護に分けて置いています。上表は介護給付（要介護1から要介護5まで）の分です。居宅療養管理指導、福祉用具貸与、特定福祉用具購入、住宅改修、小規模多機能型居宅</t>
+          <t>認知症初期集中支援推進事業について、専門医の確保を含む担当チームの体制を3町及び広域連合で確かめ、休止している町の再開の見通しを整理します。あわせて、対応件数と会議の開催回数を町ごとに同じ様式で記録し</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr"/>
@@ -1990,11 +1990,11 @@
         <v>38</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>843</v>
+        <v>691</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>注）「―」は令和7年度に要支援1・2の利用がないもの（介護予防訪問入浴介護・介護予防認知症対応型通所介護）及び月単位の包括報酬により回数の計上がないもの（介護予防通所リハビリテーション）です。介護予防</t>
+          <t>認知症の通所・居住の受け皿が減少していることを踏まえ、既存の小規模多機能型居宅介護（5事業所・全国比4.00倍）との役割分担を検討します。</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr"/>
@@ -2004,11 +2004,11 @@
         <v>39</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>867</v>
+        <v>694</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>【認知症総合支援事業の実施状況】</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr"/>
@@ -2018,11 +2018,11 @@
         <v>40</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>868</v>
+        <v>700</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業は包括的支援事業（社会保障充実分）として実施しています。事業ごとの利用者実人数及び事業費を把握できていないため量の見込みは掲げられません。構成3町の実施状況は次のとおりです。</t>
+          <t>施設・居住系の定員は縮小しています。介護老人福祉施設の定員は平成29年度234人から令和2年度以降160人へ31.6％減少し、要支援・要介護者1人当たりでは平成30年度0.126人から令和7年度0.0</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr"/>
@@ -2032,11 +2032,11 @@
         <v>41</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>870</v>
+        <v>787</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではあり</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護被保険者証の電子資格確認が導入され、要介護認定等の申請の代行を行うことができる者に特定施設入居者生活介護を行う指定居宅サービス事業者</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr"/>
@@ -2046,11 +2046,11 @@
         <v>42</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>893</v>
+        <v>831</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行いま</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr"/>
@@ -2060,11 +2060,11 @@
         <v>43</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>900</v>
+        <v>839</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
+          <t>注）1人1月当たりの回（日）数は、要支援と要介護に分けて置いています。上表は介護給付（要介護1から要介護5まで）の分です。居宅療養管理指導、福祉用具貸与、特定福祉用具購入、住宅改修、小規模多機能型居宅</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr"/>
@@ -2074,11 +2074,11 @@
         <v>44</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>905</v>
+        <v>849</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
+          <t>注）「―」は令和7年度に要支援1・2の利用がないもの（介護予防訪問入浴介護・介護予防認知症対応型通所介護）及び月単位の包括報酬により回数の計上がないもの（介護予防通所リハビリテーション）です。介護予防</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr"/>
@@ -2088,11 +2088,11 @@
         <v>45</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>909</v>
+        <v>873</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
+          <t>【認知症総合支援事業の実施状況】</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr"/>
@@ -2102,11 +2102,11 @@
         <v>46</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>912</v>
+        <v>874</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条第2項第1号により本計画が定める必要利用定員総数は、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の3つのサービスです。介護</t>
+          <t>認知症総合支援事業は包括的支援事業（社会保障充実分）として実施しています。事業ごとの利用者実人数及び事業費を把握できていないため量の見込みは掲げられません。構成3町の実施状況は次のとおりです。</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr"/>
@@ -2116,11 +2116,11 @@
         <v>47</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>994</v>
+        <v>876</v>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増</t>
+          <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではあり</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr"/>
@@ -2130,12 +2130,11 @@
         <v>48</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>995</v>
+        <v>899</v>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行いま</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr"/>
@@ -2145,17 +2144,102 @@
         <v>49</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>1045</v>
+        <v>906</v>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
+          <t>介護保険法第117条第2項第1号は、日常生活圏域ごとに、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の必要利用定員総数を計画に定めることを求め</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr"/>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>911</v>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>注）認知症対応型共同生活介護は、東川町の1事業所の定員が未確認です（第2章第3節6）。また地域包括ケア「見える化」システムD26による令和6年度の定員は5事業所99人であり、事業所数・定員とも本表と一</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr"/>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>915</v>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr"/>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>918</v>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>介護保険法第117条第2項第1号により本計画が定める必要利用定員総数は、認知症対応型共同生活介護、地域密着型特定施設入居者生活介護及び地域密着型介護老人福祉施設入所者生活介護の3つのサービスです。介護</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr"/>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>1001</v>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr"/>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>1052</v>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
           <t>本計画は介護保険法に基づく広域連合の介護保険事業計画であり、構成3町の高齢者福祉計画とは分離して策定します。一方、介護予防、生活支援、認知症、家族介護、医療・介護連携等は相互に影響するため、次の役割分</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr"/>
-    </row>
-    <row r="64" ht="34" customHeight="1">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr"/>
+    </row>
+    <row r="70" ht="34" customHeight="1">
+      <c r="A70" s="8" t="inlineStr">
         <is>
           <t>注）段落の番号は素案の先頭からの通し番号です。素案を改訂すると番号は動きます。本表は素案の実物（docx）から数えているため、素案を改めれば本表も追随します。</t>
         </is>
@@ -2164,9 +2248,9 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A70:D70"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A64:D64"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2248,12 +2332,13 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の名宛人は「市町村」であり広域連合は該当しない。広域連合は介護保険法上の保険者としての事務を共同処理する特別地方公共団体であり、一体のものとして定めても同法第13条の市町村計画としての効力は生じない。法定の計画でないものを法定の計画として掲げることになる。</t>
+          <t>認知症基本法第13条第1項の名宛人は「市町村」であり広域連合は該当しない。広域連合は介護保険法上の保険者としての事務を共同処理する特別地方公共団体であり、広域連合が自らの計画として定めることは同法第13条の市町村計画には当たらない。ただし、国の認知症施策推進基本計画は、市町村計画を介護保険事業計画等と一体のものとして策定する際に複数の市町村による広域の計画が策定される可能性があるとしており、3町が共同して市町村計画を定め本計画と一体のものとする道は残る（案B′。令和8年10月24日に原典により確認）。</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>採らない</t>
+          <t>採らない
+（案B′は要協議）</t>
         </is>
       </c>
     </row>
@@ -2532,12 +2617,14 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="62" customHeight="1">
+    <row r="22" ht="132" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>注1）新たな節・章は起こしていません。いずれも既にある節への加筆です（令和8年9月10日 発注者指示）。
 注2）認知症総合支援事業の実施主体（確認事項No.130②）と意見の聴取（同③）は決着していません。素案では実施主体を従前どおり「3町・広域連合」と併記し、意見の聴取は［要協議］を残しています。
-注3）認知症基本法の条文を受領していないため、素案には条番号（第13条）のみを書き、項番号は書いていません（確認事項No.149）。</t>
+注3）認知症基本法の条文及び国の認知症施策推進基本計画は令和8年10月に原典により確認しました（確認事項No.149は解決）。素案には項番号（第13条第1項・第2項・第3項）を書いています。
+注4）国の認知症施策推進基本計画（令和6年12月3日 閣議決定）により、次の3件を素案に加えました。①重点目標4件及び指標の3つの観点（プロセス指標・アウトプット指標・アウトカム指標）②市町村計画を介護保険事業計画等と一体のものとして策定することが差し支えないこと及び複数の市町村による広域の計画が策定される可能性があること（案B′）③意見を聴く相手が認知症の人及び家族等のほかサービス提供者・公共交通事業者等・金融機関・小売業者・学識経験を有する者・地域住民その他の関係者に及ぶこと。
+注5）同計画及び策定の手引きは、認知症施策推進計画には介護保険の給付及び地域支援事業に位置づけられた事業以外にも広範な施策が位置づけられる必要があるとしています。本計画が扱えるのは介護保険の事業の範囲であり、交通・金融・小売・教育その他の分野にわたる施策は構成3町の市町村計画において定めることになります［要協議］。</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4687,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>素案の実物（1083段落）から数えた</t>
+          <t>素案の実物（1090段落）から数えた</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>言及3件</t>
+          <t>言及5件</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -4630,7 +4717,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>49段落</t>
+          <t>55段落</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -4855,7 +4942,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>5件</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
